--- a/etf_screener/data/top-performer-b (1).xlsx
+++ b/etf_screener/data/top-performer-b (1).xlsx
@@ -61,676 +61,676 @@
     <t>Total Return (1Y)</t>
   </si>
   <si>
+    <t>DFEN</t>
+  </si>
+  <si>
+    <t>Direxion Daily Aerospace &amp; Defense Bull 3X Shares Direxion Daily Aerospace</t>
+  </si>
+  <si>
+    <t>EQRR</t>
+  </si>
+  <si>
+    <t>ProShares Equities for Rising Rates ETF</t>
+  </si>
+  <si>
+    <t>FAS</t>
+  </si>
+  <si>
+    <t>Direxion Daily Financial Bull 3X Shares</t>
+  </si>
+  <si>
+    <t>FITE</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® S&amp;P Kensho Future Security ETF</t>
+  </si>
+  <si>
+    <t>LOUP</t>
+  </si>
+  <si>
+    <t>Innovator Deepwater Frontier Tech ETF</t>
+  </si>
+  <si>
+    <t>QQQA</t>
+  </si>
+  <si>
+    <t>ProShares Nasdaq-100 Dorsey Wright Momentum ETF</t>
+  </si>
+  <si>
+    <t>EUAD</t>
+  </si>
+  <si>
+    <t>Select STOXX Europe Aerospace &amp; Defense ETF</t>
+  </si>
+  <si>
+    <t>PWV</t>
+  </si>
+  <si>
+    <t>Invesco Large Cap Value ETF</t>
+  </si>
+  <si>
+    <t>RSPT</t>
+  </si>
+  <si>
+    <t>Invesco S&amp;P 500® Equal Weight Technology ETF</t>
+  </si>
+  <si>
+    <t>IUS</t>
+  </si>
+  <si>
+    <t>Invesco RAFI™ Strategic US ETF</t>
+  </si>
+  <si>
+    <t>RFFC</t>
+  </si>
+  <si>
+    <t>ALPS Active Equity Opportunity ETF</t>
+  </si>
+  <si>
+    <t>XT</t>
+  </si>
+  <si>
+    <t>iShares Future Exponential Technologies ETF</t>
+  </si>
+  <si>
+    <t>THNQ</t>
+  </si>
+  <si>
+    <t>Robo Global® Artificial Intelligence ETF</t>
+  </si>
+  <si>
+    <t>QVAL</t>
+  </si>
+  <si>
+    <t>Alpha Architect U.S. Quantitative Value ETF</t>
+  </si>
+  <si>
+    <t>QVMT</t>
+  </si>
+  <si>
+    <t>Invesco S&amp;P S&amp;P 500 Concentrated QVM ETF</t>
+  </si>
+  <si>
+    <t>RWL</t>
+  </si>
+  <si>
+    <t>Invesco S&amp;P 500 Revenue ETF</t>
+  </si>
+  <si>
+    <t>DBJP</t>
+  </si>
+  <si>
+    <t>Xtrackers MSCI Japan Hedged Equity ETF</t>
+  </si>
+  <si>
+    <t>VLU</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® S&amp;P® 1500 Value Tilt ETF</t>
+  </si>
+  <si>
+    <t>NACP</t>
+  </si>
+  <si>
+    <t>Impact Shares NAACP Minority Empowerment ETF</t>
+  </si>
+  <si>
+    <t>VLUE</t>
+  </si>
+  <si>
+    <t>iShares MSCI USA Value Factor ETF</t>
+  </si>
+  <si>
+    <t>PEXL</t>
+  </si>
+  <si>
+    <t>Pacer US Export Leaders ETF</t>
+  </si>
+  <si>
+    <t>FNDX</t>
+  </si>
+  <si>
+    <t>Schwab Fundamental U.S. Large Company ETF</t>
+  </si>
+  <si>
+    <t>MGV</t>
+  </si>
+  <si>
+    <t>Vanguard Morningstar Mega Cap Value ETF</t>
+  </si>
+  <si>
+    <t>REVS</t>
+  </si>
+  <si>
+    <t>Columbia Research Enhanced Value ETF</t>
+  </si>
+  <si>
+    <t>ILDR</t>
+  </si>
+  <si>
+    <t>First Trust Innovation Leaders ETF</t>
+  </si>
+  <si>
+    <t>DVLU</t>
+  </si>
+  <si>
+    <t>First Trust Dorsey Wright Momentum &amp; Value ETF</t>
+  </si>
+  <si>
+    <t>RFDA</t>
+  </si>
+  <si>
+    <t>ALPS Dynamic US Dividend Advantage ETF</t>
+  </si>
+  <si>
+    <t>VEGN</t>
+  </si>
+  <si>
+    <t>US Vegan Climate ETF</t>
+  </si>
+  <si>
+    <t>AIVC</t>
+  </si>
+  <si>
+    <t>Amplify Bloomberg AI Equal Weight ETF</t>
+  </si>
+  <si>
+    <t>FNDB</t>
+  </si>
+  <si>
+    <t>Schwab Fundamental U.S. Broad Market ETF</t>
+  </si>
+  <si>
+    <t>MFUS</t>
+  </si>
+  <si>
+    <t>PIMCO RAFI Dynamic Multi-Factor U.S. Equity ETF</t>
+  </si>
+  <si>
+    <t>FELC</t>
+  </si>
+  <si>
+    <t>Fidelity Enhanced Large Cap Core ETF</t>
+  </si>
+  <si>
+    <t>FXL</t>
+  </si>
+  <si>
+    <t>First Trust Technology AlphaDEX® Fund</t>
+  </si>
+  <si>
+    <t>VIG</t>
+  </si>
+  <si>
+    <t>Vanguard Dividend Appreciation Index Fund ETF Shares</t>
+  </si>
+  <si>
+    <t>RPG</t>
+  </si>
+  <si>
+    <t>Invesco S&amp;P 500® Pure Growth ETF</t>
+  </si>
+  <si>
+    <t>PRF</t>
+  </si>
+  <si>
+    <t>Invesco RAFI US 1000 ETF</t>
+  </si>
+  <si>
+    <t>SPHQ</t>
+  </si>
+  <si>
+    <t>Invesco S&amp;P 500® Quality ETF</t>
+  </si>
+  <si>
+    <t>VOO</t>
+  </si>
+  <si>
+    <t>Vanguard S&amp;P 500 ETF</t>
+  </si>
+  <si>
+    <t>GREK</t>
+  </si>
+  <si>
+    <t>Global X MSCI Greece ETF</t>
+  </si>
+  <si>
+    <t>ULVM</t>
+  </si>
+  <si>
+    <t>VictoryShares US Value Momentum ETF</t>
+  </si>
+  <si>
+    <t>ROUS</t>
+  </si>
+  <si>
+    <t>Hartford Multifactor US Equity ETF</t>
+  </si>
+  <si>
+    <t>SPY</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® S&amp;P 500® ETF Trust</t>
+  </si>
+  <si>
+    <t>TDIV</t>
+  </si>
+  <si>
+    <t>First Trust NASDAQ Technology Dividend Index Fund</t>
+  </si>
+  <si>
+    <t>DXJ</t>
+  </si>
+  <si>
+    <t>WisdomTree Japan Hedged Equity Fund</t>
+  </si>
+  <si>
+    <t>SPXV</t>
+  </si>
+  <si>
+    <t>ProShares S&amp;P 500® ex-Health Care ETF</t>
+  </si>
+  <si>
+    <t>JMOM</t>
+  </si>
+  <si>
+    <t>JPMorgan U.S. Momentum Factor ETF</t>
+  </si>
+  <si>
+    <t>BBP</t>
+  </si>
+  <si>
+    <t>Virtus LifeSci Biotech Products ETF</t>
+  </si>
+  <si>
+    <t>QTEC</t>
+  </si>
+  <si>
+    <t>First Trust NASDAQ-100-Technology Sector Index Fund</t>
+  </si>
+  <si>
+    <t>SPYV</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® Portfolio S&amp;P 500 Value ETF</t>
+  </si>
+  <si>
+    <t>FEX</t>
+  </si>
+  <si>
+    <t>First Trust Large Cap Core AlphaDEX® Fund</t>
+  </si>
+  <si>
+    <t>DGRW</t>
+  </si>
+  <si>
+    <t>WisdomTree U.S. Quality Dividend Growth Fund</t>
+  </si>
+  <si>
+    <t>IGM</t>
+  </si>
+  <si>
+    <t>iShares Expanded Tech Sector ETF</t>
+  </si>
+  <si>
+    <t>SPYG</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® Portfolio S&amp;P 500 Growth ETF</t>
+  </si>
+  <si>
+    <t>PDP</t>
+  </si>
+  <si>
+    <t>Invesco Dorsey Wright Momentum ETF</t>
+  </si>
+  <si>
+    <t>MTUM</t>
+  </si>
+  <si>
+    <t>iShares MSCI USA Momentum Factor ETF</t>
+  </si>
+  <si>
+    <t>QQQM</t>
+  </si>
+  <si>
+    <t>Invesco NASDAQ 100 ETF</t>
+  </si>
+  <si>
+    <t>SPXL</t>
+  </si>
+  <si>
+    <t>Direxion Daily S&amp;P500® Bull 3X Shares</t>
+  </si>
+  <si>
+    <t>XLG</t>
+  </si>
+  <si>
+    <t>Invesco S&amp;P 500® Top 50 ETF</t>
+  </si>
+  <si>
+    <t>QQQ</t>
+  </si>
+  <si>
+    <t>Invesco QQQ Trust</t>
+  </si>
+  <si>
+    <t>SHE</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® MSCI USA Gender Diversity ETF</t>
+  </si>
+  <si>
+    <t>SPXN</t>
+  </si>
+  <si>
+    <t>ProShares S&amp;P 500® ex-Financials ETF</t>
+  </si>
+  <si>
+    <t>IQLT</t>
+  </si>
+  <si>
+    <t>iShares MSCI Intl Quality Factor ETF</t>
+  </si>
+  <si>
+    <t>CGDV</t>
+  </si>
+  <si>
+    <t>Capital Group Dividend Value ETF</t>
+  </si>
+  <si>
+    <t>XOVR</t>
+  </si>
+  <si>
+    <t>ERShares Private-Public Crossover ETF</t>
+  </si>
+  <si>
+    <t>FDTX</t>
+  </si>
+  <si>
+    <t>Fidelity Disruptive Technology ETF</t>
+  </si>
+  <si>
+    <t>RDVY</t>
+  </si>
+  <si>
+    <t>First Trust Rising Dividend Achievers ETF</t>
+  </si>
+  <si>
+    <t>RAFE</t>
+  </si>
+  <si>
+    <t>PIMCO RAFI ESG U.S. ETF PIMCO RAFI ESG U.S. ETF</t>
+  </si>
+  <si>
+    <t>HLAL</t>
+  </si>
+  <si>
+    <t>Wahed FTSE USA Shariah ETF</t>
+  </si>
+  <si>
+    <t>XNTK</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® NYSE Technology ETF</t>
+  </si>
+  <si>
+    <t>DDM</t>
+  </si>
+  <si>
+    <t>ProShares Ultra Dow30</t>
+  </si>
+  <si>
+    <t>XLK</t>
+  </si>
+  <si>
+    <t>State Street® Technology Select Sector SPDR® ETF</t>
+  </si>
+  <si>
+    <t>SPEM</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® Portfolio Emerging Markets ETF</t>
+  </si>
+  <si>
+    <t>VWO</t>
+  </si>
+  <si>
+    <t>Vanguard FTSE Emerging Markets Index Fund ETF Shares</t>
+  </si>
+  <si>
+    <t>SPMO</t>
+  </si>
+  <si>
+    <t>Invesco S&amp;P 500® Momentum ETF</t>
+  </si>
+  <si>
+    <t>PWB</t>
+  </si>
+  <si>
+    <t>Invesco Large Cap Growth ETF</t>
+  </si>
+  <si>
+    <t>FAD</t>
+  </si>
+  <si>
+    <t>First Trust Multi Cap Growth AlphaDEX® Fund</t>
+  </si>
+  <si>
+    <t>JVAL</t>
+  </si>
+  <si>
+    <t>JPMorgan U.S. Value Factor ETF</t>
+  </si>
+  <si>
+    <t>FYC</t>
+  </si>
+  <si>
+    <t>First Trust Small Cap Growth AlphaDEX® Fund</t>
+  </si>
+  <si>
+    <t>UDOW</t>
+  </si>
+  <si>
+    <t>ProShares UltraPro Dow30</t>
+  </si>
+  <si>
+    <t>AGG</t>
+  </si>
+  <si>
+    <t>iShares Core U.S. Aggregate Bond ETF</t>
+  </si>
+  <si>
+    <t>KOMP</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® S&amp;P Kensho New Economies Composite ETF</t>
+  </si>
+  <si>
+    <t>IDEV</t>
+  </si>
+  <si>
+    <t>iShares Core MSCI International Developed Markets ETF</t>
+  </si>
+  <si>
+    <t>ARTY</t>
+  </si>
+  <si>
+    <t>iShares Future AI &amp; Tech ETF</t>
+  </si>
+  <si>
+    <t>SPMB</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® Portfolio Mortgage Backed Bond ETF</t>
+  </si>
+  <si>
+    <t>VGT</t>
+  </si>
+  <si>
+    <t>Vanguard Information Technology Index Fund ETF Shares</t>
+  </si>
+  <si>
+    <t>CBSE</t>
+  </si>
+  <si>
+    <t>Clough Select Equity ETF</t>
+  </si>
+  <si>
+    <t>NXTG</t>
+  </si>
+  <si>
+    <t>First Trust IndXX NextG ETF</t>
+  </si>
+  <si>
+    <t>SPDW</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® Portfolio Developed World ex-US ETF</t>
+  </si>
+  <si>
+    <t>AIRR</t>
+  </si>
+  <si>
+    <t>First Trust RBA American Industrial RenaissanceTM ETF</t>
+  </si>
+  <si>
+    <t>SCHM</t>
+  </si>
+  <si>
+    <t>Schwab U.S. Mid-Cap ETF™</t>
+  </si>
+  <si>
+    <t>CSD</t>
+  </si>
+  <si>
+    <t>Invesco S&amp;P Spin-Off ETF</t>
+  </si>
+  <si>
+    <t>IGPT</t>
+  </si>
+  <si>
+    <t>Invesco AI and Next Gen Software ETF</t>
+  </si>
+  <si>
+    <t>TECL</t>
+  </si>
+  <si>
+    <t>Direxion Daily Technology Bull 3X Shares</t>
+  </si>
+  <si>
+    <t>SPSM</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® Portfolio S&amp;P 600™ Small Cap ETF</t>
+  </si>
+  <si>
+    <t>USXF</t>
+  </si>
+  <si>
+    <t>iShares® ESG Advanced MSCI USA ETF</t>
+  </si>
+  <si>
+    <t>BOTZ</t>
+  </si>
+  <si>
+    <t>Global X Robotics &amp; Artificial Intelligence ETF</t>
+  </si>
+  <si>
+    <t>FDVV</t>
+  </si>
+  <si>
+    <t>Fidelity High Dividend ETF</t>
+  </si>
+  <si>
+    <t>SPHB</t>
+  </si>
+  <si>
+    <t>Invesco S&amp;P 500® High Beta ETF</t>
+  </si>
+  <si>
+    <t>QTUM</t>
+  </si>
+  <si>
+    <t>Defiance Quantum ETF</t>
+  </si>
+  <si>
+    <t>TDV</t>
+  </si>
+  <si>
+    <t>ProShares S&amp;P Technology Dividend Aristocrats ETF</t>
+  </si>
+  <si>
+    <t>KNCT</t>
+  </si>
+  <si>
+    <t>Invesco Next Gen Connectivity ETF</t>
+  </si>
+  <si>
+    <t>IXN</t>
+  </si>
+  <si>
+    <t>iShares Global Tech ETF</t>
+  </si>
+  <si>
+    <t>SLYV</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® S&amp;P 600™ Small Cap Value ETF</t>
+  </si>
+  <si>
+    <t>ROM</t>
+  </si>
+  <si>
+    <t>ProShares Ultra Technology</t>
+  </si>
+  <si>
+    <t>UFOX</t>
+  </si>
+  <si>
+    <t>Defiance Space and Connective Tech ETF</t>
+  </si>
+  <si>
+    <t>SOXX</t>
+  </si>
+  <si>
+    <t>iShares Semiconductor ETF</t>
+  </si>
+  <si>
+    <t>PSCT</t>
+  </si>
+  <si>
+    <t>Invesco S&amp;P SmallCap Information Technology ETF</t>
+  </si>
+  <si>
+    <t>FTXL</t>
+  </si>
+  <si>
+    <t>First Trust Nasdaq Semiconductor ETF</t>
+  </si>
+  <si>
+    <t>PTF</t>
+  </si>
+  <si>
+    <t>Invesco Dorsey Wright Technology Momentum ETF</t>
+  </si>
+  <si>
+    <t>XSD</t>
+  </si>
+  <si>
+    <t>State Street® SPDR® S&amp;P® Semiconductor ETF</t>
+  </si>
+  <si>
     <t>SOXL</t>
   </si>
   <si>
     <t>Direxion Daily Semiconductor Bull 3X Shares</t>
   </si>
   <si>
-    <t>XSD</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® S&amp;P® Semiconductor ETF</t>
-  </si>
-  <si>
-    <t>XOVR</t>
-  </si>
-  <si>
-    <t>ERShares Private-Public Crossover ETF</t>
-  </si>
-  <si>
-    <t>TECL</t>
-  </si>
-  <si>
-    <t>Direxion Daily Technology Bull 3X Shares</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
     <t>ProShares Ultra Semiconductors</t>
-  </si>
-  <si>
-    <t>LOUP</t>
-  </si>
-  <si>
-    <t>Innovator Deepwater Frontier Tech ETF</t>
-  </si>
-  <si>
-    <t>UFOX</t>
-  </si>
-  <si>
-    <t>Defiance Space and Connective Tech ETF</t>
-  </si>
-  <si>
-    <t>QTUM</t>
-  </si>
-  <si>
-    <t>Defiance Quantum ETF</t>
-  </si>
-  <si>
-    <t>ROM</t>
-  </si>
-  <si>
-    <t>ProShares Ultra Technology</t>
-  </si>
-  <si>
-    <t>THNQ</t>
-  </si>
-  <si>
-    <t>Robo Global® Artificial Intelligence ETF</t>
-  </si>
-  <si>
-    <t>FTXL</t>
-  </si>
-  <si>
-    <t>First Trust Nasdaq Semiconductor ETF</t>
-  </si>
-  <si>
-    <t>AIVC</t>
-  </si>
-  <si>
-    <t>Amplify Bloomberg AI Equal Weight ETF</t>
-  </si>
-  <si>
-    <t>FDTX</t>
-  </si>
-  <si>
-    <t>Fidelity Disruptive Technology ETF</t>
-  </si>
-  <si>
-    <t>FXL</t>
-  </si>
-  <si>
-    <t>First Trust Technology AlphaDEX® Fund</t>
-  </si>
-  <si>
-    <t>KOMP</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® S&amp;P Kensho New Economies Composite ETF</t>
-  </si>
-  <si>
-    <t>PTF</t>
-  </si>
-  <si>
-    <t>Invesco Dorsey Wright Technology Momentum ETF</t>
-  </si>
-  <si>
-    <t>BBP</t>
-  </si>
-  <si>
-    <t>Virtus LifeSci Biotech Products ETF</t>
-  </si>
-  <si>
-    <t>FITE</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® S&amp;P Kensho Future Security ETF</t>
-  </si>
-  <si>
-    <t>ILDR</t>
-  </si>
-  <si>
-    <t>First Trust Innovation Leaders ETF</t>
-  </si>
-  <si>
-    <t>SOXX</t>
-  </si>
-  <si>
-    <t>iShares Semiconductor ETF</t>
-  </si>
-  <si>
-    <t>AIRR</t>
-  </si>
-  <si>
-    <t>First Trust RBA American Industrial RenaissanceTM ETF</t>
-  </si>
-  <si>
-    <t>PSCT</t>
-  </si>
-  <si>
-    <t>Invesco S&amp;P SmallCap Information Technology ETF</t>
-  </si>
-  <si>
-    <t>RSPT</t>
-  </si>
-  <si>
-    <t>Invesco S&amp;P 500® Equal Weight Technology ETF</t>
-  </si>
-  <si>
-    <t>BOTZ</t>
-  </si>
-  <si>
-    <t>Global X Robotics &amp; Artificial Intelligence ETF</t>
-  </si>
-  <si>
-    <t>SPXL</t>
-  </si>
-  <si>
-    <t>Direxion Daily S&amp;P500® Bull 3X Shares</t>
-  </si>
-  <si>
-    <t>QTEC</t>
-  </si>
-  <si>
-    <t>First Trust NASDAQ-100-Technology Sector Index Fund</t>
-  </si>
-  <si>
-    <t>ARTY</t>
-  </si>
-  <si>
-    <t>iShares Future AI &amp; Tech ETF</t>
-  </si>
-  <si>
-    <t>SPHB</t>
-  </si>
-  <si>
-    <t>Invesco S&amp;P 500® High Beta ETF</t>
-  </si>
-  <si>
-    <t>XNTK</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® NYSE Technology ETF</t>
-  </si>
-  <si>
-    <t>VGT</t>
-  </si>
-  <si>
-    <t>Vanguard Information Technology Index Fund ETF Shares</t>
-  </si>
-  <si>
-    <t>NXTG</t>
-  </si>
-  <si>
-    <t>First Trust IndXX NextG ETF</t>
-  </si>
-  <si>
-    <t>XLK</t>
-  </si>
-  <si>
-    <t>State Street® Technology Select Sector SPDR® ETF</t>
-  </si>
-  <si>
-    <t>XT</t>
-  </si>
-  <si>
-    <t>iShares Future Exponential Technologies ETF</t>
-  </si>
-  <si>
-    <t>TDV</t>
-  </si>
-  <si>
-    <t>ProShares S&amp;P Technology Dividend Aristocrats ETF</t>
-  </si>
-  <si>
-    <t>QVAL</t>
-  </si>
-  <si>
-    <t>Alpha Architect U.S. Quantitative Value ETF</t>
-  </si>
-  <si>
-    <t>TDIV</t>
-  </si>
-  <si>
-    <t>First Trust NASDAQ Technology Dividend Index Fund</t>
-  </si>
-  <si>
-    <t>FAD</t>
-  </si>
-  <si>
-    <t>First Trust Multi Cap Growth AlphaDEX® Fund</t>
-  </si>
-  <si>
-    <t>SCHM</t>
-  </si>
-  <si>
-    <t>Schwab U.S. Mid-Cap ETF™</t>
-  </si>
-  <si>
-    <t>IGM</t>
-  </si>
-  <si>
-    <t>iShares Expanded Tech Sector ETF</t>
-  </si>
-  <si>
-    <t>CBSE</t>
-  </si>
-  <si>
-    <t>Clough Select Equity ETF</t>
-  </si>
-  <si>
-    <t>DBJP</t>
-  </si>
-  <si>
-    <t>Xtrackers MSCI Japan Hedged Equity ETF</t>
-  </si>
-  <si>
-    <t>IQLT</t>
-  </si>
-  <si>
-    <t>iShares MSCI Intl Quality Factor ETF</t>
-  </si>
-  <si>
-    <t>QQQ</t>
-  </si>
-  <si>
-    <t>Invesco QQQ Trust</t>
-  </si>
-  <si>
-    <t>QQQM</t>
-  </si>
-  <si>
-    <t>Invesco NASDAQ 100 ETF</t>
-  </si>
-  <si>
-    <t>IDEV</t>
-  </si>
-  <si>
-    <t>iShares Core MSCI International Developed Markets ETF</t>
-  </si>
-  <si>
-    <t>IXN</t>
-  </si>
-  <si>
-    <t>iShares Global Tech ETF</t>
-  </si>
-  <si>
-    <t>SPDW</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® Portfolio Developed World ex-US ETF</t>
-  </si>
-  <si>
-    <t>JVAL</t>
-  </si>
-  <si>
-    <t>JPMorgan U.S. Value Factor ETF</t>
-  </si>
-  <si>
-    <t>USXF</t>
-  </si>
-  <si>
-    <t>iShares® ESG Advanced MSCI USA ETF</t>
-  </si>
-  <si>
-    <t>JMOM</t>
-  </si>
-  <si>
-    <t>JPMorgan U.S. Momentum Factor ETF</t>
-  </si>
-  <si>
-    <t>SPEM</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® Portfolio Emerging Markets ETF</t>
-  </si>
-  <si>
-    <t>DXJ</t>
-  </si>
-  <si>
-    <t>WisdomTree Japan Hedged Equity Fund</t>
-  </si>
-  <si>
-    <t>QQQA</t>
-  </si>
-  <si>
-    <t>ProShares Nasdaq-100 Dorsey Wright Momentum ETF</t>
-  </si>
-  <si>
-    <t>KNCT</t>
-  </si>
-  <si>
-    <t>Invesco Next Gen Connectivity ETF</t>
-  </si>
-  <si>
-    <t>SLYV</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® S&amp;P 600™ Small Cap Value ETF</t>
-  </si>
-  <si>
-    <t>DFEN</t>
-  </si>
-  <si>
-    <t>Direxion Daily Aerospace &amp; Defense Bull 3X Shares Direxion Daily Aerospace</t>
-  </si>
-  <si>
-    <t>VWO</t>
-  </si>
-  <si>
-    <t>Vanguard FTSE Emerging Markets Index Fund ETF Shares</t>
-  </si>
-  <si>
-    <t>RPG</t>
-  </si>
-  <si>
-    <t>Invesco S&amp;P 500® Pure Growth ETF</t>
-  </si>
-  <si>
-    <t>FDVV</t>
-  </si>
-  <si>
-    <t>Fidelity High Dividend ETF</t>
-  </si>
-  <si>
-    <t>FEX</t>
-  </si>
-  <si>
-    <t>First Trust Large Cap Core AlphaDEX® Fund</t>
-  </si>
-  <si>
-    <t>PEXL</t>
-  </si>
-  <si>
-    <t>Pacer US Export Leaders ETF</t>
-  </si>
-  <si>
-    <t>RAFE</t>
-  </si>
-  <si>
-    <t>PIMCO RAFI ESG U.S. ETF PIMCO RAFI ESG U.S. ETF</t>
-  </si>
-  <si>
-    <t>GREK</t>
-  </si>
-  <si>
-    <t>Global X MSCI Greece ETF</t>
-  </si>
-  <si>
-    <t>VLUE</t>
-  </si>
-  <si>
-    <t>iShares MSCI USA Value Factor ETF</t>
-  </si>
-  <si>
-    <t>SPXN</t>
-  </si>
-  <si>
-    <t>ProShares S&amp;P 500® ex-Financials ETF</t>
-  </si>
-  <si>
-    <t>SHE</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® MSCI USA Gender Diversity ETF</t>
-  </si>
-  <si>
-    <t>SPSM</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® Portfolio S&amp;P 600™ Small Cap ETF</t>
-  </si>
-  <si>
-    <t>HLAL</t>
-  </si>
-  <si>
-    <t>Wahed FTSE USA Shariah ETF</t>
-  </si>
-  <si>
-    <t>UDOW</t>
-  </si>
-  <si>
-    <t>ProShares UltraPro Dow30</t>
-  </si>
-  <si>
-    <t>SPYG</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® Portfolio S&amp;P 500 Growth ETF</t>
-  </si>
-  <si>
-    <t>FYC</t>
-  </si>
-  <si>
-    <t>First Trust Small Cap Growth AlphaDEX® Fund</t>
-  </si>
-  <si>
-    <t>SPXV</t>
-  </si>
-  <si>
-    <t>ProShares S&amp;P 500® ex-Health Care ETF</t>
-  </si>
-  <si>
-    <t>CSD</t>
-  </si>
-  <si>
-    <t>Invesco S&amp;P Spin-Off ETF</t>
-  </si>
-  <si>
-    <t>PDP</t>
-  </si>
-  <si>
-    <t>Invesco Dorsey Wright Momentum ETF</t>
-  </si>
-  <si>
-    <t>SPY</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® S&amp;P 500® ETF Trust</t>
-  </si>
-  <si>
-    <t>VOO</t>
-  </si>
-  <si>
-    <t>Vanguard S&amp;P 500 ETF</t>
-  </si>
-  <si>
-    <t>ROUS</t>
-  </si>
-  <si>
-    <t>Hartford Multifactor US Equity ETF</t>
-  </si>
-  <si>
-    <t>NACP</t>
-  </si>
-  <si>
-    <t>Impact Shares NAACP Minority Empowerment ETF</t>
-  </si>
-  <si>
-    <t>DGRW</t>
-  </si>
-  <si>
-    <t>WisdomTree U.S. Quality Dividend Growth Fund</t>
-  </si>
-  <si>
-    <t>XLG</t>
-  </si>
-  <si>
-    <t>Invesco S&amp;P 500® Top 50 ETF</t>
-  </si>
-  <si>
-    <t>FELC</t>
-  </si>
-  <si>
-    <t>Fidelity Enhanced Large Cap Core ETF</t>
-  </si>
-  <si>
-    <t>CGDV</t>
-  </si>
-  <si>
-    <t>Capital Group Dividend Value ETF</t>
-  </si>
-  <si>
-    <t>IUS</t>
-  </si>
-  <si>
-    <t>Invesco RAFI™ Strategic US ETF</t>
-  </si>
-  <si>
-    <t>DDM</t>
-  </si>
-  <si>
-    <t>ProShares Ultra Dow30</t>
-  </si>
-  <si>
-    <t>EUAD</t>
-  </si>
-  <si>
-    <t>Select STOXX Europe Aerospace &amp; Defense ETF</t>
-  </si>
-  <si>
-    <t>REVS</t>
-  </si>
-  <si>
-    <t>Columbia Research Enhanced Value ETF</t>
-  </si>
-  <si>
-    <t>PRF</t>
-  </si>
-  <si>
-    <t>Invesco RAFI US 1000 ETF</t>
-  </si>
-  <si>
-    <t>MFUS</t>
-  </si>
-  <si>
-    <t>PIMCO RAFI Dynamic Multi-Factor U.S. Equity ETF</t>
-  </si>
-  <si>
-    <t>SPYV</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® Portfolio S&amp;P 500 Value ETF</t>
-  </si>
-  <si>
-    <t>FNDB</t>
-  </si>
-  <si>
-    <t>Schwab Fundamental U.S. Broad Market ETF</t>
-  </si>
-  <si>
-    <t>MGV</t>
-  </si>
-  <si>
-    <t>Vanguard Morningstar Mega Cap Value ETF</t>
-  </si>
-  <si>
-    <t>RFDA</t>
-  </si>
-  <si>
-    <t>ALPS Dynamic US Dividend Advantage ETF</t>
-  </si>
-  <si>
-    <t>RFFC</t>
-  </si>
-  <si>
-    <t>ALPS Active Equity Opportunity ETF</t>
-  </si>
-  <si>
-    <t>IGPT</t>
-  </si>
-  <si>
-    <t>Invesco AI and Next Gen Software ETF</t>
-  </si>
-  <si>
-    <t>VLU</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® S&amp;P® 1500 Value Tilt ETF</t>
-  </si>
-  <si>
-    <t>DVLU</t>
-  </si>
-  <si>
-    <t>First Trust Dorsey Wright Momentum &amp; Value ETF</t>
-  </si>
-  <si>
-    <t>FNDX</t>
-  </si>
-  <si>
-    <t>Schwab Fundamental U.S. Large Company ETF</t>
-  </si>
-  <si>
-    <t>SPMO</t>
-  </si>
-  <si>
-    <t>Invesco S&amp;P 500® Momentum ETF</t>
-  </si>
-  <si>
-    <t>PWB</t>
-  </si>
-  <si>
-    <t>Invesco Large Cap Growth ETF</t>
-  </si>
-  <si>
-    <t>RWL</t>
-  </si>
-  <si>
-    <t>Invesco S&amp;P 500 Revenue ETF</t>
-  </si>
-  <si>
-    <t>MTUM</t>
-  </si>
-  <si>
-    <t>iShares MSCI USA Momentum Factor ETF</t>
-  </si>
-  <si>
-    <t>VIG</t>
-  </si>
-  <si>
-    <t>Vanguard Dividend Appreciation Index Fund ETF Shares</t>
-  </si>
-  <si>
-    <t>SPMB</t>
-  </si>
-  <si>
-    <t>State Street® SPDR® Portfolio Mortgage Backed Bond ETF</t>
-  </si>
-  <si>
-    <t>EQRR</t>
-  </si>
-  <si>
-    <t>ProShares Equities for Rising Rates ETF</t>
-  </si>
-  <si>
-    <t>ULVM</t>
-  </si>
-  <si>
-    <t>VictoryShares US Value Momentum ETF</t>
-  </si>
-  <si>
-    <t>SPHQ</t>
-  </si>
-  <si>
-    <t>Invesco S&amp;P 500® Quality ETF</t>
-  </si>
-  <si>
-    <t>AGG</t>
-  </si>
-  <si>
-    <t>iShares Core U.S. Aggregate Bond ETF</t>
-  </si>
-  <si>
-    <t>VEGN</t>
-  </si>
-  <si>
-    <t>US Vegan Climate ETF</t>
-  </si>
-  <si>
-    <t>RDVY</t>
-  </si>
-  <si>
-    <t>First Trust Rising Dividend Achievers ETF</t>
-  </si>
-  <si>
-    <t>PWV</t>
-  </si>
-  <si>
-    <t>Invesco Large Cap Value ETF</t>
-  </si>
-  <si>
-    <t>QVMT</t>
-  </si>
-  <si>
-    <t>Invesco S&amp;P S&amp;P 500 Concentrated QVM ETF</t>
-  </si>
-  <si>
-    <t>FAS</t>
-  </si>
-  <si>
-    <t>Direxion Daily Financial Bull 3X Shares</t>
   </si>
 </sst>
 </file>
@@ -1188,43 +1188,43 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>140.25</v>
+        <v>87.22</v>
       </c>
       <c r="E2">
-        <v>5.985</v>
+        <v>1.833</v>
       </c>
       <c r="F2">
-        <v>7.92</v>
+        <v>1.57</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1.4894112171282303</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1.2800000000000011</v>
       </c>
       <c r="I2">
-        <v>44.3958</v>
+        <v>14.05354</v>
       </c>
       <c r="J2">
-        <v>-26.91858</v>
+        <v>4.37826</v>
       </c>
       <c r="K2">
-        <v>-27.34212</v>
+        <v>24.73271</v>
       </c>
       <c r="L2">
-        <v>-9.10457</v>
+        <v>33.43202</v>
       </c>
       <c r="M2">
-        <v>146.52643</v>
+        <v>6.92793</v>
       </c>
       <c r="N2">
-        <v>180.18314</v>
+        <v>40.91468</v>
       </c>
       <c r="O2">
-        <v>212.59794</v>
+        <v>34.52834</v>
       </c>
       <c r="P2">
-        <v>436.07806</v>
+        <v>62.60521</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -1238,43 +1238,43 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>544.67</v>
+        <v>85.36</v>
       </c>
       <c r="E3">
-        <v>4.6597</v>
+        <v>1.536</v>
       </c>
       <c r="F3">
-        <v>24.25</v>
+        <v>1.2913</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1.535643340589274</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1.2909999999999968</v>
       </c>
       <c r="I3">
-        <v>13.4214</v>
+        <v>1.94709</v>
       </c>
       <c r="J3">
-        <v>-8.38963</v>
+        <v>5.16098</v>
       </c>
       <c r="K3">
-        <v>-10.88974</v>
+        <v>7.08583</v>
       </c>
       <c r="L3">
-        <v>-1.68382</v>
+        <v>12.5373</v>
       </c>
       <c r="M3">
-        <v>47.46152</v>
+        <v>23.09303</v>
       </c>
       <c r="N3">
-        <v>50.42456</v>
+        <v>34.53524</v>
       </c>
       <c r="O3">
-        <v>58.53511</v>
+        <v>31.46274</v>
       </c>
       <c r="P3">
-        <v>91.78241</v>
+        <v>41.99946</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -1288,43 +1288,43 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>20.13</v>
+        <v>182</v>
       </c>
       <c r="E4">
-        <v>4.5171</v>
+        <v>1.2574</v>
       </c>
       <c r="F4">
-        <v>0.87</v>
+        <v>2.26</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1.35323272261514</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2.430000000000007</v>
       </c>
       <c r="I4">
-        <v>2.92734</v>
+        <v>3.43723</v>
       </c>
       <c r="J4">
-        <v>-9.63745</v>
+        <v>7.28273</v>
       </c>
       <c r="K4">
-        <v>0.5618</v>
+        <v>31.86004</v>
       </c>
       <c r="L4">
-        <v>4.29025</v>
+        <v>35.88726</v>
       </c>
       <c r="M4">
-        <v>12.7075</v>
+        <v>12.96755</v>
       </c>
       <c r="N4">
-        <v>-3.24324</v>
+        <v>19.03162</v>
       </c>
       <c r="O4">
-        <v>-1.79551</v>
+        <v>7.80041</v>
       </c>
       <c r="P4">
-        <v>-2.08851</v>
+        <v>25.21906</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -1338,43 +1338,43 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>211.64</v>
+        <v>117.29</v>
       </c>
       <c r="E5">
-        <v>4.0409</v>
+        <v>1.172</v>
       </c>
       <c r="F5">
-        <v>8.22</v>
+        <v>1.3587</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1.1722490101871017</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1.3590000000000089</v>
       </c>
       <c r="I5">
-        <v>36.76264</v>
+        <v>8.71048</v>
       </c>
       <c r="J5">
-        <v>4.63309</v>
+        <v>3.80548</v>
       </c>
       <c r="K5">
-        <v>1.57407</v>
+        <v>6.28655</v>
       </c>
       <c r="L5">
-        <v>25.62323</v>
+        <v>19.45183</v>
       </c>
       <c r="M5">
-        <v>114.01019</v>
+        <v>30.08418</v>
       </c>
       <c r="N5">
-        <v>56.78897</v>
+        <v>35.00352</v>
       </c>
       <c r="O5">
-        <v>74.71435</v>
+        <v>36.03551</v>
       </c>
       <c r="P5">
-        <v>118.25358</v>
+        <v>51.11316</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -1388,43 +1388,43 @@
         <v>1</v>
       </c>
       <c r="D6">
-        <v>93.67</v>
+        <v>94.375</v>
       </c>
       <c r="E6">
-        <v>3.457</v>
+        <v>1.0122</v>
       </c>
       <c r="F6">
-        <v>3.13</v>
+        <v>0.9457</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1.141356767763367</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1.0649999999999977</v>
       </c>
       <c r="I6">
-        <v>31.91765</v>
+        <v>9.60092</v>
       </c>
       <c r="J6">
-        <v>3.40531</v>
+        <v>-2.14048</v>
       </c>
       <c r="K6">
-        <v>2.51257</v>
+        <v>0.64304</v>
       </c>
       <c r="L6">
-        <v>11.75962</v>
+        <v>6.95226</v>
       </c>
       <c r="M6">
-        <v>84.36758</v>
+        <v>25.8579</v>
       </c>
       <c r="N6">
-        <v>58.02764</v>
+        <v>18.37738</v>
       </c>
       <c r="O6">
-        <v>72.80504</v>
+        <v>22.17668</v>
       </c>
       <c r="P6">
-        <v>112.67541</v>
+        <v>44.11196</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -1438,43 +1438,43 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>93.31</v>
+        <v>72.73</v>
       </c>
       <c r="E7">
-        <v>3.105</v>
+        <v>1.0039</v>
       </c>
       <c r="F7">
-        <v>2.81</v>
+        <v>0.7229</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1.0040690488424722</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.722999999999999</v>
       </c>
       <c r="I7">
-        <v>3.55187</v>
+        <v>1.06482</v>
       </c>
       <c r="J7">
-        <v>-8.83048</v>
+        <v>-3.93744</v>
       </c>
       <c r="K7">
-        <v>-3.63116</v>
+        <v>-4.31987</v>
       </c>
       <c r="L7">
-        <v>2.23104</v>
+        <v>3.3818</v>
       </c>
       <c r="M7">
-        <v>20.51286</v>
+        <v>35.17582</v>
       </c>
       <c r="N7">
-        <v>12.7342</v>
+        <v>48.49105</v>
       </c>
       <c r="O7">
-        <v>16.98797</v>
+        <v>43.97912</v>
       </c>
       <c r="P7">
-        <v>37.47466</v>
+        <v>59.81266</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -1488,43 +1488,43 @@
         <v>1</v>
       </c>
       <c r="D8">
-        <v>86.79</v>
+        <v>47.445</v>
       </c>
       <c r="E8">
-        <v>2.9303</v>
+        <v>0.9253</v>
       </c>
       <c r="F8">
-        <v>2.4708</v>
+        <v>0.435</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.92533503509892</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.4350000000000023</v>
       </c>
       <c r="I8">
-        <v>6.36022</v>
+        <v>4.62677</v>
       </c>
       <c r="J8">
-        <v>-6.02424</v>
+        <v>6.54622</v>
       </c>
       <c r="K8">
-        <v>-11.19624</v>
+        <v>16.44764</v>
       </c>
       <c r="L8">
-        <v>-3.95885</v>
+        <v>12.24357</v>
       </c>
       <c r="M8">
-        <v>25.39459</v>
+        <v>5.8524</v>
       </c>
       <c r="N8">
-        <v>29.42834</v>
+        <v>7.84091</v>
       </c>
       <c r="O8">
-        <v>32.4759</v>
+        <v>11.7772</v>
       </c>
       <c r="P8">
-        <v>49.85313</v>
+        <v>12.18249</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -1538,43 +1538,43 @@
         <v>1</v>
       </c>
       <c r="D9">
-        <v>153.46</v>
+        <v>80.56</v>
       </c>
       <c r="E9">
-        <v>2.8277</v>
+        <v>0.7</v>
       </c>
       <c r="F9">
-        <v>4.22</v>
+        <v>0.56</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>0.6874140732408414</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>0.5499999999999972</v>
       </c>
       <c r="I9">
-        <v>6.57038</v>
+        <v>0.03751</v>
       </c>
       <c r="J9">
-        <v>-4.84455</v>
+        <v>2.14505</v>
       </c>
       <c r="K9">
-        <v>-3.12234</v>
+        <v>6.75331</v>
       </c>
       <c r="L9">
-        <v>4.53314</v>
+        <v>11.33373</v>
       </c>
       <c r="M9">
-        <v>29.79129</v>
+        <v>14.9405</v>
       </c>
       <c r="N9">
-        <v>35.76774</v>
+        <v>24.70497</v>
       </c>
       <c r="O9">
-        <v>36.69384</v>
+        <v>21.56038</v>
       </c>
       <c r="P9">
-        <v>63.40594</v>
+        <v>31.91716</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -1588,43 +1588,43 @@
         <v>1</v>
       </c>
       <c r="D10">
-        <v>148.36</v>
+        <v>65</v>
       </c>
       <c r="E10">
-        <v>2.7068</v>
+        <v>0.5414</v>
       </c>
       <c r="F10">
-        <v>3.91</v>
+        <v>0.35</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.5413766434648016</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>0.3499999999999943</v>
       </c>
       <c r="I10">
-        <v>10.94819</v>
+        <v>7.05415</v>
       </c>
       <c r="J10">
-        <v>0.46745</v>
+        <v>5.53379</v>
       </c>
       <c r="K10">
-        <v>2.90676</v>
+        <v>4.90197</v>
       </c>
       <c r="L10">
-        <v>13.86066</v>
+        <v>14.72432</v>
       </c>
       <c r="M10">
-        <v>61.10261</v>
+        <v>38.29117</v>
       </c>
       <c r="N10">
-        <v>50.01528</v>
+        <v>43.11476</v>
       </c>
       <c r="O10">
-        <v>53.05675</v>
+        <v>42.30314</v>
       </c>
       <c r="P10">
-        <v>77.36584</v>
+        <v>59.32866</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -1638,43 +1638,43 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>90.54</v>
+        <v>69.78</v>
       </c>
       <c r="E11">
-        <v>2.6738</v>
+        <v>0.5331</v>
       </c>
       <c r="F11">
-        <v>2.3578</v>
+        <v>0.37</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.38843331894690836</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>0.269999999999996</v>
       </c>
       <c r="I11">
-        <v>12.74795</v>
+        <v>2.31154</v>
       </c>
       <c r="J11">
-        <v>0.7906</v>
+        <v>4.18291</v>
       </c>
       <c r="K11">
-        <v>4.79098</v>
+        <v>7.60998</v>
       </c>
       <c r="L11">
-        <v>18.5756</v>
+        <v>9.6755</v>
       </c>
       <c r="M11">
-        <v>49.8321</v>
+        <v>15.70776</v>
       </c>
       <c r="N11">
-        <v>33.544</v>
+        <v>25.94312</v>
       </c>
       <c r="O11">
-        <v>40.40277</v>
+        <v>22.45096</v>
       </c>
       <c r="P11">
-        <v>61.55566</v>
+        <v>36.0714</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -1688,43 +1688,43 @@
         <v>1</v>
       </c>
       <c r="D12">
-        <v>236.49</v>
+        <v>77.13</v>
       </c>
       <c r="E12">
-        <v>2.5764</v>
+        <v>0.5213</v>
       </c>
       <c r="F12">
-        <v>5.94</v>
+        <v>0.4</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.16753029181437992</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>0.12899999999999068</v>
       </c>
       <c r="I12">
-        <v>5.85482</v>
+        <v>2.99243</v>
       </c>
       <c r="J12">
-        <v>-9.67464</v>
+        <v>2.36185</v>
       </c>
       <c r="K12">
-        <v>-5.54344</v>
+        <v>5.44731</v>
       </c>
       <c r="L12">
-        <v>-1.18671</v>
+        <v>6.08772</v>
       </c>
       <c r="M12">
-        <v>49.38139</v>
+        <v>10.27061</v>
       </c>
       <c r="N12">
-        <v>86.11277</v>
+        <v>18.3661</v>
       </c>
       <c r="O12">
-        <v>78.25372</v>
+        <v>15.31605</v>
       </c>
       <c r="P12">
-        <v>141.96631</v>
+        <v>26.58517</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -1738,43 +1738,43 @@
         <v>1</v>
       </c>
       <c r="D13">
-        <v>110.94</v>
+        <v>83.23</v>
       </c>
       <c r="E13">
-        <v>2.5039</v>
+        <v>0.5193</v>
       </c>
       <c r="F13">
-        <v>2.71</v>
+        <v>0.43</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.470787059391599</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>0.39000000000000057</v>
       </c>
       <c r="I13">
-        <v>8.06603</v>
+        <v>3.96794</v>
       </c>
       <c r="J13">
-        <v>-1.51954</v>
+        <v>0.86451</v>
       </c>
       <c r="K13">
-        <v>-3.38896</v>
+        <v>3.60727</v>
       </c>
       <c r="L13">
-        <v>9.34289</v>
+        <v>6.45385</v>
       </c>
       <c r="M13">
-        <v>52.92187</v>
+        <v>15.93977</v>
       </c>
       <c r="N13">
-        <v>54.74257</v>
+        <v>21.664</v>
       </c>
       <c r="O13">
-        <v>58.95262</v>
+        <v>19.24328</v>
       </c>
       <c r="P13">
-        <v>94.3722</v>
+        <v>36.13245</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -1788,43 +1788,43 @@
         <v>1</v>
       </c>
       <c r="D14">
-        <v>55.09</v>
+        <v>90.98085</v>
       </c>
       <c r="E14">
-        <v>2.3905</v>
+        <v>0.4869</v>
       </c>
       <c r="F14">
-        <v>1.2862</v>
+        <v>0.44085</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>0.4869118621603683</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>0.4408499999999975</v>
       </c>
       <c r="I14">
-        <v>15.52586</v>
+        <v>6.97124</v>
       </c>
       <c r="J14">
-        <v>0.4504</v>
+        <v>3.40961</v>
       </c>
       <c r="K14">
-        <v>1.63845</v>
+        <v>6.12964</v>
       </c>
       <c r="L14">
-        <v>14.17696</v>
+        <v>15.72343</v>
       </c>
       <c r="M14">
-        <v>45.24611</v>
+        <v>45.79771</v>
       </c>
       <c r="N14">
-        <v>28.97795</v>
+        <v>37.5298</v>
       </c>
       <c r="O14">
-        <v>33.16325</v>
+        <v>42.19635</v>
       </c>
       <c r="P14">
-        <v>39.0094</v>
+        <v>61.25957</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -1838,43 +1838,43 @@
         <v>1</v>
       </c>
       <c r="D15">
-        <v>216.75</v>
+        <v>60.615</v>
       </c>
       <c r="E15">
-        <v>2.3613</v>
+        <v>0.4737</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>0.2858</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>0.47406719819655785</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>0.28600000000000136</v>
       </c>
       <c r="I15">
-        <v>7.23008</v>
+        <v>3.25478</v>
       </c>
       <c r="J15">
-        <v>1.91659</v>
+        <v>7.11977</v>
       </c>
       <c r="K15">
-        <v>2.31074</v>
+        <v>9.17188</v>
       </c>
       <c r="L15">
-        <v>8.76201</v>
+        <v>12.1552</v>
       </c>
       <c r="M15">
-        <v>25.23818</v>
+        <v>12.99445</v>
       </c>
       <c r="N15">
-        <v>25.4163</v>
+        <v>31.38147</v>
       </c>
       <c r="O15">
-        <v>25.84884</v>
+        <v>24.79377</v>
       </c>
       <c r="P15">
-        <v>32.87238</v>
+        <v>43.69568</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -1888,43 +1888,43 @@
         <v>1</v>
       </c>
       <c r="D16">
-        <v>70.6</v>
+        <v>65.5</v>
       </c>
       <c r="E16">
-        <v>2.2892</v>
+        <v>0.4708</v>
       </c>
       <c r="F16">
-        <v>1.58</v>
+        <v>0.3069</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>0.47090945346893404</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>0.30700000000000216</v>
       </c>
       <c r="I16">
-        <v>8.88563</v>
+        <v>0.74097</v>
       </c>
       <c r="J16">
-        <v>-0.61982</v>
+        <v>-1.01623</v>
       </c>
       <c r="K16">
-        <v>-0.67219</v>
+        <v>-0.51285</v>
       </c>
       <c r="L16">
-        <v>3.09047</v>
+        <v>1.90422</v>
       </c>
       <c r="M16">
-        <v>15.56436</v>
+        <v>7.1717</v>
       </c>
       <c r="N16">
-        <v>9.98643</v>
+        <v>20.93377</v>
       </c>
       <c r="O16">
-        <v>16.04095</v>
+        <v>15.38387</v>
       </c>
       <c r="P16">
-        <v>26.22256</v>
+        <v>32.34853</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -1938,43 +1938,43 @@
         <v>1</v>
       </c>
       <c r="D17">
-        <v>108.1659</v>
+        <v>134.68</v>
       </c>
       <c r="E17">
-        <v>2.2219</v>
+        <v>0.4175</v>
       </c>
       <c r="F17">
-        <v>2.3511</v>
+        <v>0.56</v>
       </c>
       <c r="G17">
-        <v>-0.00009245049276419547</v>
+        <v>0.4175365344467658</v>
       </c>
       <c r="H17">
-        <v>-0.00010000000000331966</v>
+        <v>0.5600000000000023</v>
       </c>
       <c r="I17">
-        <v>24.0551</v>
+        <v>1.89883</v>
       </c>
       <c r="J17">
-        <v>-7.19634</v>
+        <v>3.13653</v>
       </c>
       <c r="K17">
-        <v>-13.46201</v>
+        <v>5.97293</v>
       </c>
       <c r="L17">
-        <v>-11.12611</v>
+        <v>8.87066</v>
       </c>
       <c r="M17">
-        <v>25.99856</v>
+        <v>11.75354</v>
       </c>
       <c r="N17">
-        <v>29.49853</v>
+        <v>21.03648</v>
       </c>
       <c r="O17">
-        <v>37.77952</v>
+        <v>17.97075</v>
       </c>
       <c r="P17">
-        <v>51.89765</v>
+        <v>31.39128</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -1988,43 +1988,43 @@
         <v>1</v>
       </c>
       <c r="D18">
-        <v>100.365</v>
+        <v>116.02</v>
       </c>
       <c r="E18">
-        <v>2.094</v>
+        <v>0.3795</v>
       </c>
       <c r="F18">
-        <v>2.0585</v>
+        <v>0.4386</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>0.3798202126647052</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>0.43899999999999295</v>
       </c>
       <c r="I18">
-        <v>0.57452</v>
+        <v>1.78411</v>
       </c>
       <c r="J18">
-        <v>-2.05017</v>
+        <v>-0.03836</v>
       </c>
       <c r="K18">
-        <v>14.60463</v>
+        <v>2.62059</v>
       </c>
       <c r="L18">
-        <v>10.99561</v>
+        <v>6.28897</v>
       </c>
       <c r="M18">
-        <v>22.84719</v>
+        <v>12.83147</v>
       </c>
       <c r="N18">
-        <v>30.87569</v>
+        <v>27.08322</v>
       </c>
       <c r="O18">
-        <v>21.72699</v>
+        <v>22.93881</v>
       </c>
       <c r="P18">
-        <v>53.30606</v>
+        <v>44.7932</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -2038,43 +2038,43 @@
         <v>1</v>
       </c>
       <c r="D19">
-        <v>115.9313</v>
+        <v>248.63</v>
       </c>
       <c r="E19">
-        <v>2.0788</v>
+        <v>0.3309</v>
       </c>
       <c r="F19">
-        <v>2.3609</v>
+        <v>0.82</v>
       </c>
       <c r="G19">
-        <v>0.00025877461593167326</v>
+        <v>0.3308986723699581</v>
       </c>
       <c r="H19">
-        <v>0.0002999999999957481</v>
+        <v>0.8199999999999932</v>
       </c>
       <c r="I19">
-        <v>10.83003</v>
+        <v>2.06235</v>
       </c>
       <c r="J19">
-        <v>0.76768</v>
+        <v>3.13041</v>
       </c>
       <c r="K19">
-        <v>4.20811</v>
+        <v>5.64698</v>
       </c>
       <c r="L19">
-        <v>18.67994</v>
+        <v>7.43273</v>
       </c>
       <c r="M19">
-        <v>33.51596</v>
+        <v>11.04267</v>
       </c>
       <c r="N19">
-        <v>31.46281</v>
+        <v>22.59867</v>
       </c>
       <c r="O19">
-        <v>33.37533</v>
+        <v>18.93145</v>
       </c>
       <c r="P19">
-        <v>48.45827</v>
+        <v>30.91297</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -2088,43 +2088,43 @@
         <v>1</v>
       </c>
       <c r="D20">
-        <v>39.24</v>
+        <v>60.45</v>
       </c>
       <c r="E20">
-        <v>2.0281</v>
+        <v>0.3225</v>
       </c>
       <c r="F20">
-        <v>0.78</v>
+        <v>0.1943</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>0.32195963887414136</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>0.19400000000000261</v>
       </c>
       <c r="I20">
-        <v>6.81502</v>
+        <v>3.58359</v>
       </c>
       <c r="J20">
-        <v>-1.51321</v>
+        <v>1.64953</v>
       </c>
       <c r="K20">
-        <v>1.96495</v>
+        <v>4.72497</v>
       </c>
       <c r="L20">
-        <v>5.69777</v>
+        <v>7.46959</v>
       </c>
       <c r="M20">
-        <v>22.33195</v>
+        <v>18.23874</v>
       </c>
       <c r="N20">
-        <v>15.87206</v>
+        <v>24.18965</v>
       </c>
       <c r="O20">
-        <v>16.71733</v>
+        <v>21.86222</v>
       </c>
       <c r="P20">
-        <v>26.56559</v>
+        <v>38.65432</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -2138,43 +2138,43 @@
         <v>1</v>
       </c>
       <c r="D21">
-        <v>543.27</v>
+        <v>198.24</v>
       </c>
       <c r="E21">
-        <v>2.0187</v>
+        <v>0.3087</v>
       </c>
       <c r="F21">
-        <v>10.75</v>
+        <v>0.61</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>0.30865759247078567</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>0.6100000000000136</v>
       </c>
       <c r="I21">
-        <v>14.35563</v>
+        <v>3.45729</v>
       </c>
       <c r="J21">
-        <v>-6.32621</v>
+        <v>2.97861</v>
       </c>
       <c r="K21">
-        <v>-1.65162</v>
+        <v>3.42124</v>
       </c>
       <c r="L21">
-        <v>10.02115</v>
+        <v>13.45129</v>
       </c>
       <c r="M21">
-        <v>60.64617</v>
+        <v>31.11746</v>
       </c>
       <c r="N21">
-        <v>74.17715</v>
+        <v>53.85423</v>
       </c>
       <c r="O21">
-        <v>76.4825</v>
+        <v>45.73058</v>
       </c>
       <c r="P21">
-        <v>123.45021</v>
+        <v>77.90727</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -2188,43 +2188,43 @@
         <v>1</v>
       </c>
       <c r="D22">
-        <v>123.54</v>
+        <v>73.195</v>
       </c>
       <c r="E22">
-        <v>1.9812</v>
+        <v>0.3041</v>
       </c>
       <c r="F22">
-        <v>2.4</v>
+        <v>0.2219</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>0.3042221095473589</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>0.2219999999999942</v>
       </c>
       <c r="I22">
-        <v>5.1558</v>
+        <v>3.83983</v>
       </c>
       <c r="J22">
-        <v>-4.53865</v>
+        <v>0.65413</v>
       </c>
       <c r="K22">
-        <v>-5.30718</v>
+        <v>2.95504</v>
       </c>
       <c r="L22">
-        <v>-8.12922</v>
+        <v>5.41449</v>
       </c>
       <c r="M22">
-        <v>2.35074</v>
+        <v>17.03122</v>
       </c>
       <c r="N22">
-        <v>25.07219</v>
+        <v>25.85818</v>
       </c>
       <c r="O22">
-        <v>23.35832</v>
+        <v>20.06817</v>
       </c>
       <c r="P22">
-        <v>38.64832</v>
+        <v>37.61826</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -2238,43 +2238,43 @@
         <v>1</v>
       </c>
       <c r="D23">
-        <v>83.21</v>
+        <v>32.41</v>
       </c>
       <c r="E23">
-        <v>1.9481</v>
+        <v>0.294</v>
       </c>
       <c r="F23">
-        <v>1.59</v>
+        <v>0.095</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>0.3095017022593448</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>0.09999999999999432</v>
       </c>
       <c r="I23">
-        <v>9.20652</v>
+        <v>1.86003</v>
       </c>
       <c r="J23">
-        <v>-1.99715</v>
+        <v>3.0622</v>
       </c>
       <c r="K23">
-        <v>1.62722</v>
+        <v>5.57807</v>
       </c>
       <c r="L23">
-        <v>6.71845</v>
+        <v>7.57408</v>
       </c>
       <c r="M23">
-        <v>38.57791</v>
+        <v>11.74759</v>
       </c>
       <c r="N23">
-        <v>39.94228</v>
+        <v>23.47541</v>
       </c>
       <c r="O23">
-        <v>45.67945</v>
+        <v>19.67383</v>
       </c>
       <c r="P23">
-        <v>81.59902</v>
+        <v>33.02769</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -2288,43 +2288,43 @@
         <v>1</v>
       </c>
       <c r="D24">
-        <v>64.65</v>
+        <v>167.23</v>
       </c>
       <c r="E24">
-        <v>1.8431</v>
+        <v>0.2638</v>
       </c>
       <c r="F24">
-        <v>1.17</v>
+        <v>0.44</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>0.2457738880230168</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>0.4099999999999966</v>
       </c>
       <c r="I24">
-        <v>9.31783</v>
+        <v>2.24333</v>
       </c>
       <c r="J24">
-        <v>4.11985</v>
+        <v>1.64524</v>
       </c>
       <c r="K24">
-        <v>3.74992</v>
+        <v>6.26387</v>
       </c>
       <c r="L24">
-        <v>14.78754</v>
+        <v>9.77258</v>
       </c>
       <c r="M24">
-        <v>41.86276</v>
+        <v>9.99448</v>
       </c>
       <c r="N24">
-        <v>39.38819</v>
+        <v>23.21847</v>
       </c>
       <c r="O24">
-        <v>40.74033</v>
+        <v>19.36915</v>
       </c>
       <c r="P24">
-        <v>57.34697</v>
+        <v>30.71171</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -2338,43 +2338,43 @@
         <v>1</v>
       </c>
       <c r="D25">
-        <v>37.61</v>
+        <v>33.95</v>
       </c>
       <c r="E25">
-        <v>1.8138</v>
+        <v>0.2593</v>
       </c>
       <c r="F25">
-        <v>0.67</v>
+        <v>0.0878</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>0.259878329691102</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>0.08800000000000097</v>
       </c>
       <c r="I25">
-        <v>10.35503</v>
+        <v>2.05005</v>
       </c>
       <c r="J25">
-        <v>-0.55985</v>
+        <v>4.70152</v>
       </c>
       <c r="K25">
-        <v>-3.94265</v>
+        <v>7.56276</v>
       </c>
       <c r="L25">
-        <v>-3.09457</v>
+        <v>9.9026</v>
       </c>
       <c r="M25">
-        <v>3.95064</v>
+        <v>12.83333</v>
       </c>
       <c r="N25">
-        <v>2.04085</v>
+        <v>24.05389</v>
       </c>
       <c r="O25">
-        <v>3.03225</v>
+        <v>19.86544</v>
       </c>
       <c r="P25">
-        <v>10.42901</v>
+        <v>29.87911</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -2388,43 +2388,43 @@
         <v>1</v>
       </c>
       <c r="D26">
-        <v>296.33</v>
+        <v>39.3401</v>
       </c>
       <c r="E26">
-        <v>1.7617</v>
+        <v>0.2551</v>
       </c>
       <c r="F26">
-        <v>5.13</v>
+        <v>0.1001</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>0.2550968399592192</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>0.10009999999999764</v>
       </c>
       <c r="I26">
-        <v>17.18997</v>
+        <v>7.95705</v>
       </c>
       <c r="J26">
-        <v>8.68109</v>
+        <v>2.32255</v>
       </c>
       <c r="K26">
-        <v>11.97735</v>
+        <v>4.11577</v>
       </c>
       <c r="L26">
-        <v>16.79853</v>
+        <v>8.58488</v>
       </c>
       <c r="M26">
-        <v>37.7288</v>
+        <v>24.91239</v>
       </c>
       <c r="N26">
-        <v>34.15887</v>
+        <v>18.45921</v>
       </c>
       <c r="O26">
-        <v>33.4679</v>
+        <v>19.17933</v>
       </c>
       <c r="P26">
-        <v>63.99038</v>
+        <v>30.39574</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -2438,43 +2438,43 @@
         <v>1</v>
       </c>
       <c r="D27">
-        <v>316.59</v>
+        <v>41.784115</v>
       </c>
       <c r="E27">
-        <v>1.7026</v>
+        <v>0.2303</v>
       </c>
       <c r="F27">
-        <v>5.3</v>
+        <v>0.096015</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>0.23055795432737838</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>0.09611499999999751</v>
       </c>
       <c r="I27">
-        <v>10.56395</v>
+        <v>1.95695</v>
       </c>
       <c r="J27">
-        <v>0.13014</v>
+        <v>4.51354</v>
       </c>
       <c r="K27">
-        <v>3.40616</v>
+        <v>6.81019</v>
       </c>
       <c r="L27">
-        <v>13.47043</v>
+        <v>11.365</v>
       </c>
       <c r="M27">
-        <v>43.50521</v>
+        <v>10.95141</v>
       </c>
       <c r="N27">
-        <v>32.69478</v>
+        <v>23.03274</v>
       </c>
       <c r="O27">
-        <v>37.06471</v>
+        <v>17.07051</v>
       </c>
       <c r="P27">
-        <v>49.96523</v>
+        <v>41.5286</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -2488,43 +2488,43 @@
         <v>1</v>
       </c>
       <c r="D28">
-        <v>72.78</v>
+        <v>73.13</v>
       </c>
       <c r="E28">
-        <v>1.6764</v>
+        <v>0.2209</v>
       </c>
       <c r="F28">
-        <v>1.2</v>
+        <v>0.1612</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>0.2206416423412701</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>0.16100000000000136</v>
       </c>
       <c r="I28">
-        <v>17.72728</v>
+        <v>1.66945</v>
       </c>
       <c r="J28">
-        <v>1.57306</v>
+        <v>2.19956</v>
       </c>
       <c r="K28">
-        <v>2.01487</v>
+        <v>4.38835</v>
       </c>
       <c r="L28">
-        <v>11.10636</v>
+        <v>7.56915</v>
       </c>
       <c r="M28">
-        <v>51.21944</v>
+        <v>13.2825</v>
       </c>
       <c r="N28">
-        <v>45.74896</v>
+        <v>18.03308</v>
       </c>
       <c r="O28">
-        <v>50.02942</v>
+        <v>16.03823</v>
       </c>
       <c r="P28">
-        <v>69.46255</v>
+        <v>25.74644</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
@@ -2538,43 +2538,43 @@
         <v>1</v>
       </c>
       <c r="D29">
-        <v>147.9</v>
+        <v>77.73</v>
       </c>
       <c r="E29">
-        <v>1.5866</v>
+        <v>0.2127</v>
       </c>
       <c r="F29">
-        <v>2.31</v>
+        <v>0.165</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>0.21272481144847064</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>0.16500000000000625</v>
       </c>
       <c r="I29">
-        <v>10.33328</v>
+        <v>4.00278</v>
       </c>
       <c r="J29">
-        <v>0.31791</v>
+        <v>0.54842</v>
       </c>
       <c r="K29">
-        <v>3.76706</v>
+        <v>3.36958</v>
       </c>
       <c r="L29">
-        <v>7.82852</v>
+        <v>11.16575</v>
       </c>
       <c r="M29">
-        <v>26.25013</v>
+        <v>28.49218</v>
       </c>
       <c r="N29">
-        <v>31.22832</v>
+        <v>30.89737</v>
       </c>
       <c r="O29">
-        <v>27.25434</v>
+        <v>28.37098</v>
       </c>
       <c r="P29">
-        <v>46.97898</v>
+        <v>39.97789</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -2588,43 +2588,43 @@
         <v>1</v>
       </c>
       <c r="D30">
-        <v>362.45</v>
+        <v>111.275</v>
       </c>
       <c r="E30">
-        <v>1.5864</v>
+        <v>0.2108</v>
       </c>
       <c r="F30">
-        <v>5.66</v>
+        <v>0.2341</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>0.30196502614026316</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>0.33500000000000796</v>
       </c>
       <c r="I30">
-        <v>12.86845</v>
+        <v>7.20438</v>
       </c>
       <c r="J30">
-        <v>-1.41357</v>
+        <v>3.25716</v>
       </c>
       <c r="K30">
-        <v>1.57675</v>
+        <v>-0.90931</v>
       </c>
       <c r="L30">
-        <v>11.10473</v>
+        <v>12.22534</v>
       </c>
       <c r="M30">
-        <v>37.23275</v>
+        <v>56.84682</v>
       </c>
       <c r="N30">
-        <v>25.25807</v>
+        <v>60.43207</v>
       </c>
       <c r="O30">
-        <v>29.19256</v>
+        <v>63.03236</v>
       </c>
       <c r="P30">
-        <v>52.58138</v>
+        <v>98.02542</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -2638,43 +2638,43 @@
         <v>1</v>
       </c>
       <c r="D31">
-        <v>121.45</v>
+        <v>31.64</v>
       </c>
       <c r="E31">
-        <v>1.5468</v>
+        <v>0.2059</v>
       </c>
       <c r="F31">
-        <v>1.85</v>
+        <v>0.065</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>0.20585906571655194</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>0.06500000000000128</v>
       </c>
       <c r="I31">
-        <v>10.70933</v>
+        <v>1.97028</v>
       </c>
       <c r="J31">
-        <v>4.33153</v>
+        <v>3.03525</v>
       </c>
       <c r="K31">
-        <v>3.97666</v>
+        <v>5.72309</v>
       </c>
       <c r="L31">
-        <v>12.19123</v>
+        <v>7.55332</v>
       </c>
       <c r="M31">
-        <v>35.50265</v>
+        <v>11.60349</v>
       </c>
       <c r="N31">
-        <v>23.53787</v>
+        <v>23.6431</v>
       </c>
       <c r="O31">
-        <v>27.37314</v>
+        <v>19.80036</v>
       </c>
       <c r="P31">
-        <v>40.76688</v>
+        <v>32.91344</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
@@ -2688,43 +2688,43 @@
         <v>1</v>
       </c>
       <c r="D32">
-        <v>152.51</v>
+        <v>66.695</v>
       </c>
       <c r="E32">
-        <v>1.5094</v>
+        <v>0.2031</v>
       </c>
       <c r="F32">
-        <v>2.2678</v>
+        <v>0.1352</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>0.20282451923075553</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>0.1349999999999909</v>
       </c>
       <c r="I32">
-        <v>3.17221</v>
+        <v>2.30415</v>
       </c>
       <c r="J32">
-        <v>0.32717</v>
+        <v>1.66387</v>
       </c>
       <c r="K32">
-        <v>-1.10658</v>
+        <v>3.92219</v>
       </c>
       <c r="L32">
-        <v>6.06354</v>
+        <v>6.31976</v>
       </c>
       <c r="M32">
-        <v>30.91066</v>
+        <v>10.17458</v>
       </c>
       <c r="N32">
-        <v>41.74547</v>
+        <v>21.45</v>
       </c>
       <c r="O32">
-        <v>39.99292</v>
+        <v>18.62707</v>
       </c>
       <c r="P32">
-        <v>56.91313</v>
+        <v>26.34555</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -2738,43 +2738,43 @@
         <v>1</v>
       </c>
       <c r="D33">
-        <v>187.97</v>
+        <v>44.04</v>
       </c>
       <c r="E33">
-        <v>1.4245</v>
+        <v>0.1934</v>
       </c>
       <c r="F33">
-        <v>2.64</v>
+        <v>0.085</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>0.18198362147406347</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>0.0799999999999983</v>
       </c>
       <c r="I33">
-        <v>5.5127</v>
+        <v>3.3031</v>
       </c>
       <c r="J33">
-        <v>0.97669</v>
+        <v>4.492</v>
       </c>
       <c r="K33">
-        <v>2.95471</v>
+        <v>6.6229</v>
       </c>
       <c r="L33">
-        <v>9.1562</v>
+        <v>7.91226</v>
       </c>
       <c r="M33">
-        <v>31.66306</v>
+        <v>14.52087</v>
       </c>
       <c r="N33">
-        <v>28.76612</v>
+        <v>18.51891</v>
       </c>
       <c r="O33">
-        <v>29.069</v>
+        <v>15.71799</v>
       </c>
       <c r="P33">
-        <v>41.62906</v>
+        <v>26.31844</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -2788,43 +2788,43 @@
         <v>1</v>
       </c>
       <c r="D34">
-        <v>82.84</v>
+        <v>217.13</v>
       </c>
       <c r="E34">
-        <v>1.4078</v>
+        <v>0.1753</v>
       </c>
       <c r="F34">
-        <v>1.15</v>
+        <v>0.38</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>0.17531718569780644</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>0.37999999999999545</v>
       </c>
       <c r="I34">
-        <v>6.12003</v>
+        <v>8.48882</v>
       </c>
       <c r="J34">
-        <v>-0.39536</v>
+        <v>6.99028</v>
       </c>
       <c r="K34">
-        <v>2.56523</v>
+        <v>4.84386</v>
       </c>
       <c r="L34">
-        <v>6.39007</v>
+        <v>12.10007</v>
       </c>
       <c r="M34">
-        <v>17.38171</v>
+        <v>28.33895</v>
       </c>
       <c r="N34">
-        <v>18.80937</v>
+        <v>28.2934</v>
       </c>
       <c r="O34">
-        <v>18.04398</v>
+        <v>28.96474</v>
       </c>
       <c r="P34">
-        <v>34.61955</v>
+        <v>36.7718</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -2838,43 +2838,43 @@
         <v>1</v>
       </c>
       <c r="D35">
-        <v>104.12</v>
+        <v>245.68</v>
       </c>
       <c r="E35">
-        <v>1.3827</v>
+        <v>0.1753</v>
       </c>
       <c r="F35">
-        <v>1.42</v>
+        <v>0.43</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>0.18350120295233743</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>0.45000000000001705</v>
       </c>
       <c r="I35">
-        <v>6.59531</v>
+        <v>2.56764</v>
       </c>
       <c r="J35">
-        <v>3.0129</v>
+        <v>2.65779</v>
       </c>
       <c r="K35">
-        <v>2.48972</v>
+        <v>5.60061</v>
       </c>
       <c r="L35">
-        <v>4.86433</v>
+        <v>7.98011</v>
       </c>
       <c r="M35">
-        <v>17.25361</v>
+        <v>7.72247</v>
       </c>
       <c r="N35">
-        <v>18.24847</v>
+        <v>15.14052</v>
       </c>
       <c r="O35">
-        <v>19.33324</v>
+        <v>12.51089</v>
       </c>
       <c r="P35">
-        <v>25.81685</v>
+        <v>21.06756</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -2888,43 +2888,43 @@
         <v>1</v>
       </c>
       <c r="D36">
-        <v>60.3292</v>
+        <v>58.53</v>
       </c>
       <c r="E36">
-        <v>1.3738</v>
+        <v>0.1711</v>
       </c>
       <c r="F36">
-        <v>0.8176</v>
+        <v>0.1</v>
       </c>
       <c r="G36">
-        <v>0.0003315155232136019</v>
+        <v>0.18829168093118698</v>
       </c>
       <c r="H36">
-        <v>0.00019999999999953388</v>
+        <v>0.10999999999999943</v>
       </c>
       <c r="I36">
-        <v>1.27546</v>
+        <v>4.396</v>
       </c>
       <c r="J36">
-        <v>6.04458</v>
+        <v>-0.94947</v>
       </c>
       <c r="K36">
-        <v>7.67419</v>
+        <v>1.21297</v>
       </c>
       <c r="L36">
-        <v>9.36206</v>
+        <v>3.74643</v>
       </c>
       <c r="M36">
-        <v>11.44433</v>
+        <v>19.52888</v>
       </c>
       <c r="N36">
-        <v>30.78192</v>
+        <v>25.82245</v>
       </c>
       <c r="O36">
-        <v>23.08177</v>
+        <v>25.26586</v>
       </c>
       <c r="P36">
-        <v>40.79835</v>
+        <v>26.24215</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -2938,43 +2938,43 @@
         <v>1</v>
       </c>
       <c r="D37">
-        <v>117.06</v>
+        <v>56.025</v>
       </c>
       <c r="E37">
-        <v>1.3506</v>
+        <v>0.1878</v>
       </c>
       <c r="F37">
-        <v>1.56</v>
+        <v>0.105</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>0.16988555078683631</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>0.09499999999999886</v>
       </c>
       <c r="I37">
-        <v>5.21715</v>
+        <v>2.13699</v>
       </c>
       <c r="J37">
-        <v>1.9677</v>
+        <v>2.86976</v>
       </c>
       <c r="K37">
-        <v>-0.6764</v>
+        <v>5.81336</v>
       </c>
       <c r="L37">
-        <v>3.60884</v>
+        <v>7.70252</v>
       </c>
       <c r="M37">
-        <v>18.27396</v>
+        <v>12.64282</v>
       </c>
       <c r="N37">
-        <v>19.31056</v>
+        <v>24.06109</v>
       </c>
       <c r="O37">
-        <v>20.21648</v>
+        <v>20.0627</v>
       </c>
       <c r="P37">
-        <v>29.77155</v>
+        <v>33.49554</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
@@ -2988,43 +2988,43 @@
         <v>1</v>
       </c>
       <c r="D38">
-        <v>191.69</v>
+        <v>86.11</v>
       </c>
       <c r="E38">
-        <v>1.3214</v>
+        <v>0.1512</v>
       </c>
       <c r="F38">
-        <v>2.5</v>
+        <v>0.13</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>0.15121554030475218</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>0.12999999999999545</v>
       </c>
       <c r="I38">
-        <v>2.98621</v>
+        <v>1.55881</v>
       </c>
       <c r="J38">
-        <v>-2.2954</v>
+        <v>-0.79594</v>
       </c>
       <c r="K38">
-        <v>3.32761</v>
+        <v>1.50299</v>
       </c>
       <c r="L38">
-        <v>2.40969</v>
+        <v>5.2073</v>
       </c>
       <c r="M38">
-        <v>12.29635</v>
+        <v>8.32588</v>
       </c>
       <c r="N38">
-        <v>18.77789</v>
+        <v>18.12838</v>
       </c>
       <c r="O38">
-        <v>16.87761</v>
+        <v>15.31372</v>
       </c>
       <c r="P38">
-        <v>25.70418</v>
+        <v>22.03449</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -3038,43 +3038,43 @@
         <v>1</v>
       </c>
       <c r="D39">
-        <v>36.09</v>
+        <v>711.59</v>
       </c>
       <c r="E39">
-        <v>1.3195</v>
+        <v>0.1407</v>
       </c>
       <c r="F39">
-        <v>0.47</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>0.12100575480857362</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>0.8600000000000136</v>
       </c>
       <c r="I39">
-        <v>5.12445</v>
+        <v>3.58912</v>
       </c>
       <c r="J39">
-        <v>-0.13908</v>
+        <v>3.4399</v>
       </c>
       <c r="K39">
-        <v>3.40913</v>
+        <v>5.21104</v>
       </c>
       <c r="L39">
-        <v>4.58048</v>
+        <v>6.02939</v>
       </c>
       <c r="M39">
-        <v>13.75374</v>
+        <v>12.53903</v>
       </c>
       <c r="N39">
-        <v>23.30624</v>
+        <v>16.28428</v>
       </c>
       <c r="O39">
-        <v>20.11335</v>
+        <v>14.06822</v>
       </c>
       <c r="P39">
-        <v>27.51792</v>
+        <v>23.78882</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -3088,43 +3088,43 @@
         <v>1</v>
       </c>
       <c r="D40">
-        <v>163.72</v>
+        <v>81.9</v>
       </c>
       <c r="E40">
-        <v>1.2618</v>
+        <v>0.1345</v>
       </c>
       <c r="F40">
-        <v>2.04</v>
+        <v>0.11</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>0.13449076904266954</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>0.10999999999999943</v>
       </c>
       <c r="I40">
-        <v>10.973</v>
+        <v>2.31539</v>
       </c>
       <c r="J40">
-        <v>3.32592</v>
+        <v>5.00963</v>
       </c>
       <c r="K40">
-        <v>3.6057</v>
+        <v>12.46895</v>
       </c>
       <c r="L40">
-        <v>9.89913</v>
+        <v>12.9007</v>
       </c>
       <c r="M40">
-        <v>33.37879</v>
+        <v>9.81433</v>
       </c>
       <c r="N40">
-        <v>23.33708</v>
+        <v>34.63458</v>
       </c>
       <c r="O40">
-        <v>25.65267</v>
+        <v>24.8102</v>
       </c>
       <c r="P40">
-        <v>41.20643</v>
+        <v>30.37637</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -3138,43 +3138,43 @@
         <v>1</v>
       </c>
       <c r="D41">
-        <v>47.9876</v>
+        <v>109.78</v>
       </c>
       <c r="E41">
-        <v>1.2322</v>
+        <v>0.128</v>
       </c>
       <c r="F41">
-        <v>0.5841</v>
+        <v>0.1403</v>
       </c>
       <c r="G41">
-        <v>-0.0008335417187610815</v>
+        <v>0.12769062385990568</v>
       </c>
       <c r="H41">
-        <v>-0.00039999999999906777</v>
+        <v>0.14000000000000057</v>
       </c>
       <c r="I41">
-        <v>4.48753</v>
+        <v>1.11852</v>
       </c>
       <c r="J41">
-        <v>-5.72752</v>
+        <v>2.3493</v>
       </c>
       <c r="K41">
-        <v>-0.89469</v>
+        <v>5.79074</v>
       </c>
       <c r="L41">
-        <v>-0.70442</v>
+        <v>9.10098</v>
       </c>
       <c r="M41">
-        <v>16.98173</v>
+        <v>12.4106</v>
       </c>
       <c r="N41">
-        <v>19.43423</v>
+        <v>23.85914</v>
       </c>
       <c r="O41">
-        <v>20.59068</v>
+        <v>21.36136</v>
       </c>
       <c r="P41">
-        <v>23.58709</v>
+        <v>30.86964</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -3188,43 +3188,43 @@
         <v>1</v>
       </c>
       <c r="D42">
-        <v>115.5814</v>
+        <v>68.37553</v>
       </c>
       <c r="E42">
-        <v>1.2008</v>
+        <v>0.1252</v>
       </c>
       <c r="F42">
-        <v>1.3714</v>
+        <v>0.08553</v>
       </c>
       <c r="G42">
-        <v>0.0003460776425182926</v>
+        <v>0.12524527749303183</v>
       </c>
       <c r="H42">
-        <v>0.00039999999999906777</v>
+        <v>0.08552999999999145</v>
       </c>
       <c r="I42">
-        <v>3.15194</v>
+        <v>2.26412</v>
       </c>
       <c r="J42">
-        <v>-1.72421</v>
+        <v>2.55468</v>
       </c>
       <c r="K42">
-        <v>2.06664</v>
+        <v>4.21407</v>
       </c>
       <c r="L42">
-        <v>9.12023</v>
+        <v>7.27985</v>
       </c>
       <c r="M42">
-        <v>12.2224</v>
+        <v>12.37103</v>
       </c>
       <c r="N42">
-        <v>25.76659</v>
+        <v>20.37078</v>
       </c>
       <c r="O42">
-        <v>22.27518</v>
+        <v>19.05994</v>
       </c>
       <c r="P42">
-        <v>45.12308</v>
+        <v>28.52201</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -3238,43 +3238,43 @@
         <v>1</v>
       </c>
       <c r="D43">
-        <v>51.67</v>
+        <v>774.17</v>
       </c>
       <c r="E43">
-        <v>1.1947</v>
+        <v>0.1255</v>
       </c>
       <c r="F43">
-        <v>0.61</v>
+        <v>0.97</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>0.11251066911517531</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>0.8700000000000045</v>
       </c>
       <c r="I43">
-        <v>3.16629</v>
+        <v>3.58397</v>
       </c>
       <c r="J43">
-        <v>3.19101</v>
+        <v>3.43149</v>
       </c>
       <c r="K43">
-        <v>7.6847</v>
+        <v>5.19497</v>
       </c>
       <c r="L43">
-        <v>6.55756</v>
+        <v>6.00954</v>
       </c>
       <c r="M43">
-        <v>9.91488</v>
+        <v>12.51027</v>
       </c>
       <c r="N43">
-        <v>18.13728</v>
+        <v>16.23323</v>
       </c>
       <c r="O43">
-        <v>14.27113</v>
+        <v>14.03179</v>
       </c>
       <c r="P43">
-        <v>24.98912</v>
+        <v>23.70186</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
@@ -3288,43 +3288,43 @@
         <v>1</v>
       </c>
       <c r="D44">
-        <v>723.03</v>
+        <v>117.2</v>
       </c>
       <c r="E44">
-        <v>1.1726</v>
+        <v>0.1196</v>
       </c>
       <c r="F44">
-        <v>8.38</v>
+        <v>0.14</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>0.11959678797198066</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>0.14000000000000057</v>
       </c>
       <c r="I44">
-        <v>8.4447</v>
+        <v>6.1169</v>
       </c>
       <c r="J44">
-        <v>0.54665</v>
+        <v>4.26498</v>
       </c>
       <c r="K44">
-        <v>1.85671</v>
+        <v>0.64722</v>
       </c>
       <c r="L44">
-        <v>5.37035</v>
+        <v>5.46059</v>
       </c>
       <c r="M44">
-        <v>20.39736</v>
+        <v>19.85012</v>
       </c>
       <c r="N44">
-        <v>15.49087</v>
+        <v>22.08352</v>
       </c>
       <c r="O44">
-        <v>17.07074</v>
+        <v>21.81853</v>
       </c>
       <c r="P44">
-        <v>28.67789</v>
+        <v>31.06594</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -3338,43 +3338,43 @@
         <v>1</v>
       </c>
       <c r="D45">
-        <v>297.7</v>
+        <v>179.44</v>
       </c>
       <c r="E45">
-        <v>1.169</v>
+        <v>0.1004</v>
       </c>
       <c r="F45">
-        <v>3.44</v>
+        <v>0.18</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>0.033448544988294276</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>0.060000000000002274</v>
       </c>
       <c r="I45">
-        <v>8.44502</v>
+        <v>1.75427</v>
       </c>
       <c r="J45">
-        <v>0.55153</v>
+        <v>1.14837</v>
       </c>
       <c r="K45">
-        <v>1.86449</v>
+        <v>4.3421</v>
       </c>
       <c r="L45">
-        <v>5.37856</v>
+        <v>7.64502</v>
       </c>
       <c r="M45">
-        <v>20.41655</v>
+        <v>12.34562</v>
       </c>
       <c r="N45">
-        <v>15.52326</v>
+        <v>32.88266</v>
       </c>
       <c r="O45">
-        <v>17.09268</v>
+        <v>25.07272</v>
       </c>
       <c r="P45">
-        <v>28.73702</v>
+        <v>48.69278</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
@@ -3388,43 +3388,43 @@
         <v>1</v>
       </c>
       <c r="D46">
-        <v>93.31</v>
+        <v>85</v>
       </c>
       <c r="E46">
-        <v>1.1162</v>
+        <v>0.1002</v>
       </c>
       <c r="F46">
-        <v>1.03</v>
+        <v>0.0851</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>0.10010010010009272</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>0.08499999999999375</v>
       </c>
       <c r="I46">
-        <v>3.6421</v>
+        <v>3.74108</v>
       </c>
       <c r="J46">
-        <v>3.2898</v>
+        <v>3.70168</v>
       </c>
       <c r="K46">
-        <v>6.20588</v>
+        <v>4.85665</v>
       </c>
       <c r="L46">
-        <v>6.36301</v>
+        <v>5.19629</v>
       </c>
       <c r="M46">
-        <v>8.886</v>
+        <v>13.17595</v>
       </c>
       <c r="N46">
-        <v>18.60017</v>
+        <v>16.33216</v>
       </c>
       <c r="O46">
-        <v>13.61073</v>
+        <v>14.64068</v>
       </c>
       <c r="P46">
-        <v>26.03202</v>
+        <v>23.01392</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
@@ -3438,43 +3438,43 @@
         <v>1</v>
       </c>
       <c r="D47">
-        <v>140.87</v>
+        <v>84.36</v>
       </c>
       <c r="E47">
-        <v>1.0908</v>
+        <v>0.0949</v>
       </c>
       <c r="F47">
-        <v>1.52</v>
+        <v>0.08</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>0.10679957280171286</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>0.09000000000000341</v>
       </c>
       <c r="I47">
-        <v>11.65628</v>
+        <v>4.33653</v>
       </c>
       <c r="J47">
-        <v>2.39798</v>
+        <v>1.57113</v>
       </c>
       <c r="K47">
-        <v>3.54539</v>
+        <v>5.25297</v>
       </c>
       <c r="L47">
-        <v>12.30033</v>
+        <v>8.3644</v>
       </c>
       <c r="M47">
-        <v>37.28297</v>
+        <v>19.91834</v>
       </c>
       <c r="N47">
-        <v>30.46668</v>
+        <v>24.89911</v>
       </c>
       <c r="O47">
-        <v>33.17858</v>
+        <v>24.0894</v>
       </c>
       <c r="P47">
-        <v>48.47248</v>
+        <v>31.50422</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
@@ -3488,43 +3488,43 @@
         <v>1</v>
       </c>
       <c r="D48">
-        <v>51.65</v>
+        <v>100.46</v>
       </c>
       <c r="E48">
-        <v>1.0565</v>
+        <v>0.0947</v>
       </c>
       <c r="F48">
-        <v>0.54</v>
+        <v>0.095</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>0.09465451103472212</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>0.09499999999999886</v>
       </c>
       <c r="I48">
-        <v>4.93874</v>
+        <v>6.97344</v>
       </c>
       <c r="J48">
-        <v>2.46259</v>
+        <v>-2.93934</v>
       </c>
       <c r="K48">
-        <v>3.5767</v>
+        <v>18.50685</v>
       </c>
       <c r="L48">
-        <v>6.3079</v>
+        <v>14.74842</v>
       </c>
       <c r="M48">
-        <v>10.86335</v>
+        <v>22.74182</v>
       </c>
       <c r="N48">
-        <v>23.03392</v>
+        <v>35.37069</v>
       </c>
       <c r="O48">
-        <v>16.99399</v>
+        <v>25.87172</v>
       </c>
       <c r="P48">
-        <v>31.34927</v>
+        <v>58.11592</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
@@ -3538,43 +3538,43 @@
         <v>1</v>
       </c>
       <c r="D49">
-        <v>59.89</v>
+        <v>316.82</v>
       </c>
       <c r="E49">
-        <v>1.0461</v>
+        <v>0.0821</v>
       </c>
       <c r="F49">
-        <v>0.62</v>
+        <v>0.26</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>0.07264916769323675</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>0.2300000000000182</v>
       </c>
       <c r="I49">
-        <v>2.70282</v>
+        <v>6.05787</v>
       </c>
       <c r="J49">
-        <v>2.01404</v>
+        <v>1.82946</v>
       </c>
       <c r="K49">
-        <v>5.14576</v>
+        <v>3.81919</v>
       </c>
       <c r="L49">
-        <v>7.75258</v>
+        <v>10.84584</v>
       </c>
       <c r="M49">
-        <v>14.74966</v>
+        <v>38.74545</v>
       </c>
       <c r="N49">
-        <v>26.58167</v>
+        <v>36.55026</v>
       </c>
       <c r="O49">
-        <v>21.71676</v>
+        <v>37.61219</v>
       </c>
       <c r="P49">
-        <v>35.06411</v>
+        <v>49.66073</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
@@ -3588,43 +3588,43 @@
         <v>1</v>
       </c>
       <c r="D50">
-        <v>69.5781</v>
+        <v>63.2</v>
       </c>
       <c r="E50">
-        <v>1.0277</v>
+        <v>0.0792</v>
       </c>
       <c r="F50">
-        <v>0.7078</v>
+        <v>0.05</v>
       </c>
       <c r="G50">
-        <v>0.0001437235907949634</v>
+        <v>0.09502692429522058</v>
       </c>
       <c r="H50">
-        <v>0.00010000000000331966</v>
+        <v>0.060000000000002274</v>
       </c>
       <c r="I50">
-        <v>4.24645</v>
+        <v>1.80119</v>
       </c>
       <c r="J50">
-        <v>1.20186</v>
+        <v>2.21307</v>
       </c>
       <c r="K50">
-        <v>5.04551</v>
+        <v>4.56994</v>
       </c>
       <c r="L50">
-        <v>5.72283</v>
+        <v>5.93296</v>
       </c>
       <c r="M50">
-        <v>17.98989</v>
+        <v>7.06994</v>
       </c>
       <c r="N50">
-        <v>21.60026</v>
+        <v>14.89436</v>
       </c>
       <c r="O50">
-        <v>19.97842</v>
+        <v>12.15045</v>
       </c>
       <c r="P50">
-        <v>25.12302</v>
+        <v>21.714</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
@@ -3638,43 +3638,43 @@
         <v>1</v>
       </c>
       <c r="D51">
-        <v>84.27</v>
+        <v>139.9689</v>
       </c>
       <c r="E51">
-        <v>1.0068</v>
+        <v>0.0779</v>
       </c>
       <c r="F51">
-        <v>0.84</v>
+        <v>0.1089</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>0.0778635778635615</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>0.10889999999997713</v>
       </c>
       <c r="I51">
-        <v>3.46964</v>
+        <v>2.73922</v>
       </c>
       <c r="J51">
-        <v>-0.81156</v>
+        <v>2.47583</v>
       </c>
       <c r="K51">
-        <v>4.14764</v>
+        <v>4.75132</v>
       </c>
       <c r="L51">
-        <v>5.96653</v>
+        <v>7.48236</v>
       </c>
       <c r="M51">
-        <v>18.659</v>
+        <v>11.06415</v>
       </c>
       <c r="N51">
-        <v>24.20577</v>
+        <v>21.1878</v>
       </c>
       <c r="O51">
-        <v>22.78626</v>
+        <v>18.49153</v>
       </c>
       <c r="P51">
-        <v>29.51873</v>
+        <v>26.54287</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
@@ -3688,43 +3688,43 @@
         <v>1</v>
       </c>
       <c r="D52">
-        <v>52.42</v>
+        <v>100.06</v>
       </c>
       <c r="E52">
-        <v>1.0019</v>
+        <v>0.065</v>
       </c>
       <c r="F52">
-        <v>0.52</v>
+        <v>0.065</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>0.03999200159968632</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>0.04000000000000625</v>
       </c>
       <c r="I52">
-        <v>5.38246</v>
+        <v>3.75169</v>
       </c>
       <c r="J52">
-        <v>1.35933</v>
+        <v>3.89499</v>
       </c>
       <c r="K52">
-        <v>1.54195</v>
+        <v>4.53951</v>
       </c>
       <c r="L52">
-        <v>2.77257</v>
+        <v>5.79383</v>
       </c>
       <c r="M52">
-        <v>7.43574</v>
+        <v>8.13576</v>
       </c>
       <c r="N52">
-        <v>13.82349</v>
+        <v>14.58911</v>
       </c>
       <c r="O52">
-        <v>12.78387</v>
+        <v>12.57354</v>
       </c>
       <c r="P52">
-        <v>23.62189</v>
+        <v>18.62716</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
@@ -3738,43 +3738,43 @@
         <v>1</v>
       </c>
       <c r="D53">
-        <v>179.38</v>
+        <v>163.84</v>
       </c>
       <c r="E53">
-        <v>0.9852</v>
+        <v>0.055</v>
       </c>
       <c r="F53">
-        <v>1.75</v>
+        <v>0.09</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>0.07329587099926982</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>0.12000000000000455</v>
       </c>
       <c r="I53">
-        <v>1.23029</v>
+        <v>6.71231</v>
       </c>
       <c r="J53">
-        <v>1.17574</v>
+        <v>4.49983</v>
       </c>
       <c r="K53">
-        <v>3.24932</v>
+        <v>4.61121</v>
       </c>
       <c r="L53">
-        <v>9.30532</v>
+        <v>8.92384</v>
       </c>
       <c r="M53">
-        <v>12.62991</v>
+        <v>30.27289</v>
       </c>
       <c r="N53">
-        <v>32.93132</v>
+        <v>27.27701</v>
       </c>
       <c r="O53">
-        <v>23.76282</v>
+        <v>26.87214</v>
       </c>
       <c r="P53">
-        <v>49.73972</v>
+        <v>40.67316</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
@@ -3788,43 +3788,43 @@
         <v>1</v>
       </c>
       <c r="D54">
-        <v>72.0071</v>
+        <v>123.06</v>
       </c>
       <c r="E54">
-        <v>0.9453</v>
+        <v>0.0488</v>
       </c>
       <c r="F54">
-        <v>0.6743</v>
+        <v>0.06</v>
       </c>
       <c r="G54">
-        <v>0.00013887538710001638</v>
+        <v>0.03251503820517497</v>
       </c>
       <c r="H54">
-        <v>0.0000999999999891088</v>
+        <v>0.04000000000000625</v>
       </c>
       <c r="I54">
-        <v>0.77044</v>
+        <v>5.09834</v>
       </c>
       <c r="J54">
-        <v>-8.81454</v>
+        <v>4.46361</v>
       </c>
       <c r="K54">
-        <v>-5.21205</v>
+        <v>5.73797</v>
       </c>
       <c r="L54">
-        <v>-0.4949</v>
+        <v>6.10225</v>
       </c>
       <c r="M54">
-        <v>33.91536</v>
+        <v>17.4963</v>
       </c>
       <c r="N54">
-        <v>45.9655</v>
+        <v>17.3922</v>
       </c>
       <c r="O54">
-        <v>42.63657</v>
+        <v>15.63572</v>
       </c>
       <c r="P54">
-        <v>58.00577</v>
+        <v>25.46207</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
@@ -3838,43 +3838,43 @@
         <v>1</v>
       </c>
       <c r="D55">
-        <v>196.3659</v>
+        <v>138.6648</v>
       </c>
       <c r="E55">
-        <v>0.9298</v>
+        <v>0.0457</v>
       </c>
       <c r="F55">
-        <v>1.8089</v>
+        <v>0.0634</v>
       </c>
       <c r="G55">
-        <v>-0.00005092531293773853</v>
+        <v>0.046753246753260834</v>
       </c>
       <c r="H55">
-        <v>-0.00010000000000331966</v>
+        <v>0.06480000000001951</v>
       </c>
       <c r="I55">
-        <v>10.28006</v>
+        <v>3.7195</v>
       </c>
       <c r="J55">
-        <v>-0.51745</v>
+        <v>-0.50255</v>
       </c>
       <c r="K55">
-        <v>1.04</v>
+        <v>-1.23993</v>
       </c>
       <c r="L55">
-        <v>10.30437</v>
+        <v>-0.50969</v>
       </c>
       <c r="M55">
-        <v>41.59277</v>
+        <v>10.34236</v>
       </c>
       <c r="N55">
-        <v>46.69791</v>
+        <v>18.19035</v>
       </c>
       <c r="O55">
-        <v>46.52433</v>
+        <v>19.08404</v>
       </c>
       <c r="P55">
-        <v>71.60255</v>
+        <v>23.78287</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
@@ -3888,43 +3888,43 @@
         <v>1</v>
       </c>
       <c r="D56">
-        <v>111</v>
+        <v>309.385</v>
       </c>
       <c r="E56">
-        <v>0.8907</v>
+        <v>0.0372</v>
       </c>
       <c r="F56">
-        <v>0.98</v>
+        <v>0.115</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>0.021013836803309753</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>0.06499999999999773</v>
       </c>
       <c r="I56">
-        <v>2.17615</v>
+        <v>3.25143</v>
       </c>
       <c r="J56">
-        <v>2.47555</v>
+        <v>-0.99041</v>
       </c>
       <c r="K56">
-        <v>7.03437</v>
+        <v>1.02989</v>
       </c>
       <c r="L56">
-        <v>7.78785</v>
+        <v>5.38898</v>
       </c>
       <c r="M56">
-        <v>13.03997</v>
+        <v>22.26455</v>
       </c>
       <c r="N56">
-        <v>26.2338</v>
+        <v>25.19748</v>
       </c>
       <c r="O56">
-        <v>22.72291</v>
+        <v>23.86852</v>
       </c>
       <c r="P56">
-        <v>39.05624</v>
+        <v>27.7592</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
@@ -3938,43 +3938,43 @@
         <v>1</v>
       </c>
       <c r="D57">
-        <v>85.94</v>
+        <v>297.73</v>
       </c>
       <c r="E57">
-        <v>0.8567</v>
+        <v>0.0202</v>
       </c>
       <c r="F57">
-        <v>0.73</v>
+        <v>0.06</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>0.010077258985565858</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>0.03000000000002956</v>
       </c>
       <c r="I57">
-        <v>21.1188</v>
+        <v>5.12006</v>
       </c>
       <c r="J57">
-        <v>1.65182</v>
+        <v>1.88576</v>
       </c>
       <c r="K57">
-        <v>26.8964</v>
+        <v>2.67499</v>
       </c>
       <c r="L57">
-        <v>49.04652</v>
+        <v>4.17874</v>
       </c>
       <c r="M57">
-        <v>20.17073</v>
+        <v>18.82317</v>
       </c>
       <c r="N57">
-        <v>42.06252</v>
+        <v>19.04479</v>
       </c>
       <c r="O57">
-        <v>36.86194</v>
+        <v>18.02435</v>
       </c>
       <c r="P57">
-        <v>63.74217</v>
+        <v>27.70102</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
@@ -3988,43 +3988,43 @@
         <v>1</v>
       </c>
       <c r="D58">
-        <v>60.47</v>
+        <v>296.32</v>
       </c>
       <c r="E58">
-        <v>0.8506</v>
+        <v>0.0169</v>
       </c>
       <c r="F58">
-        <v>0.51</v>
+        <v>0.05</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>-0.0033746161374112998</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>-0.009999999999990905</v>
       </c>
       <c r="I58">
-        <v>5.35117</v>
+        <v>10.71466</v>
       </c>
       <c r="J58">
-        <v>1.80303</v>
+        <v>9.16052</v>
       </c>
       <c r="K58">
-        <v>2.81413</v>
+        <v>13.35555</v>
       </c>
       <c r="L58">
-        <v>1.42193</v>
+        <v>14.64165</v>
       </c>
       <c r="M58">
-        <v>7.1149</v>
+        <v>31.73286</v>
       </c>
       <c r="N58">
-        <v>11.8857</v>
+        <v>40.11284</v>
       </c>
       <c r="O58">
-        <v>11.70782</v>
+        <v>35.11061</v>
       </c>
       <c r="P58">
-        <v>22.47148</v>
+        <v>62.93442</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
@@ -4038,13 +4038,13 @@
         <v>1</v>
       </c>
       <c r="D59">
-        <v>58.42</v>
+        <v>63.3</v>
       </c>
       <c r="E59">
-        <v>0.8458</v>
+        <v>0.0158</v>
       </c>
       <c r="F59">
-        <v>0.49</v>
+        <v>0.01</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -4053,28 +4053,28 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>3.7037</v>
+        <v>4.21399</v>
       </c>
       <c r="J59">
-        <v>-4.19835</v>
+        <v>3.70188</v>
       </c>
       <c r="K59">
-        <v>0.41601</v>
+        <v>1.97955</v>
       </c>
       <c r="L59">
-        <v>1.06363</v>
+        <v>1.60384</v>
       </c>
       <c r="M59">
-        <v>18.58771</v>
+        <v>8.89365</v>
       </c>
       <c r="N59">
-        <v>26.35439</v>
+        <v>8.9032</v>
       </c>
       <c r="O59">
-        <v>24.27952</v>
+        <v>7.20338</v>
       </c>
       <c r="P59">
-        <v>24.22984</v>
+        <v>17.99505</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
@@ -4088,13 +4088,13 @@
         <v>1</v>
       </c>
       <c r="D60">
-        <v>64.2</v>
+        <v>723.1</v>
       </c>
       <c r="E60">
-        <v>0.8324</v>
+        <v>0.0166</v>
       </c>
       <c r="F60">
-        <v>0.53</v>
+        <v>0.12</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -4103,28 +4103,28 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>2.24188</v>
+        <v>5.119</v>
       </c>
       <c r="J60">
-        <v>4.30658</v>
+        <v>1.88397</v>
       </c>
       <c r="K60">
-        <v>6.37422</v>
+        <v>2.66607</v>
       </c>
       <c r="L60">
-        <v>9.82673</v>
+        <v>4.16717</v>
       </c>
       <c r="M60">
-        <v>11.19221</v>
+        <v>18.80374</v>
       </c>
       <c r="N60">
-        <v>17.92372</v>
+        <v>19.00874</v>
       </c>
       <c r="O60">
-        <v>14.77299</v>
+        <v>18.00098</v>
       </c>
       <c r="P60">
-        <v>23.32294</v>
+        <v>27.64489</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
@@ -4138,43 +4138,43 @@
         <v>1</v>
       </c>
       <c r="D61">
-        <v>139.86</v>
+        <v>160.04</v>
       </c>
       <c r="E61">
-        <v>0.7947</v>
+        <v>0.0069</v>
       </c>
       <c r="F61">
-        <v>1.1027</v>
+        <v>0.0111</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>0.006873754132060863</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>0.01099999999999568</v>
       </c>
       <c r="I61">
-        <v>1.894</v>
+        <v>3.85752</v>
       </c>
       <c r="J61">
-        <v>0.74031</v>
+        <v>4.32936</v>
       </c>
       <c r="K61">
-        <v>3.92769</v>
+        <v>5.03921</v>
       </c>
       <c r="L61">
-        <v>4.93144</v>
+        <v>8.57719</v>
       </c>
       <c r="M61">
-        <v>10.19088</v>
+        <v>19.59839</v>
       </c>
       <c r="N61">
-        <v>21.41421</v>
+        <v>25.09201</v>
       </c>
       <c r="O61">
-        <v>17.55986</v>
+        <v>22.06336</v>
       </c>
       <c r="P61">
-        <v>25.42441</v>
+        <v>32.00919</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
@@ -4188,43 +4188,43 @@
         <v>1</v>
       </c>
       <c r="D62">
-        <v>72.9731</v>
+        <v>84.7</v>
       </c>
       <c r="E62">
-        <v>0.7866</v>
+        <v>-0.0077</v>
       </c>
       <c r="F62">
-        <v>0.5695</v>
+        <v>-0.0065</v>
       </c>
       <c r="G62">
-        <v>0.00013703698628714684</v>
+        <v>-0.008263779852893848</v>
       </c>
       <c r="H62">
-        <v>0.00010000000000331966</v>
+        <v>-0.006999999999990791</v>
       </c>
       <c r="I62">
-        <v>3.06347</v>
+        <v>4.0053</v>
       </c>
       <c r="J62">
-        <v>-2.11337</v>
+        <v>3.58665</v>
       </c>
       <c r="K62">
-        <v>2.06702</v>
+        <v>4.54926</v>
       </c>
       <c r="L62">
-        <v>3.55617</v>
+        <v>5.2595</v>
       </c>
       <c r="M62">
-        <v>16.02178</v>
+        <v>13.39783</v>
       </c>
       <c r="N62">
-        <v>25.38287</v>
+        <v>17.16714</v>
       </c>
       <c r="O62">
-        <v>19.03255</v>
+        <v>15.25628</v>
       </c>
       <c r="P62">
-        <v>36.7054</v>
+        <v>25.48995</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
@@ -4238,43 +4238,43 @@
         <v>1</v>
       </c>
       <c r="D63">
-        <v>49.78</v>
+        <v>51.65</v>
       </c>
       <c r="E63">
-        <v>0.7488</v>
+        <v>-0.0097</v>
       </c>
       <c r="F63">
-        <v>0.37</v>
+        <v>-0.005</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>-0.0387071801819298</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>-0.020000000000003126</v>
       </c>
       <c r="I63">
-        <v>2.25253</v>
+        <v>2.83174</v>
       </c>
       <c r="J63">
-        <v>2.95464</v>
+        <v>4.28524</v>
       </c>
       <c r="K63">
-        <v>6.10202</v>
+        <v>8.75033</v>
       </c>
       <c r="L63">
-        <v>11.4333</v>
+        <v>7.04693</v>
       </c>
       <c r="M63">
-        <v>16.40715</v>
+        <v>8.91861</v>
       </c>
       <c r="N63">
-        <v>22.50827</v>
+        <v>19.4056</v>
       </c>
       <c r="O63">
-        <v>18.90338</v>
+        <v>15.40193</v>
       </c>
       <c r="P63">
-        <v>32.75622</v>
+        <v>24.73063</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.25">
@@ -4288,43 +4288,43 @@
         <v>1</v>
       </c>
       <c r="D64">
-        <v>81.79</v>
+        <v>51.275</v>
       </c>
       <c r="E64">
-        <v>0.739</v>
+        <v>-0.0487</v>
       </c>
       <c r="F64">
-        <v>0.6</v>
+        <v>-0.025</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>-0.04873294346978281</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>-0.02499999999999858</v>
       </c>
       <c r="I64">
-        <v>4.93021</v>
+        <v>3.5534</v>
       </c>
       <c r="J64">
-        <v>6.83181</v>
+        <v>4.82322</v>
       </c>
       <c r="K64">
-        <v>12.73035</v>
+        <v>7.53137</v>
       </c>
       <c r="L64">
-        <v>17.74774</v>
+        <v>9.29043</v>
       </c>
       <c r="M64">
-        <v>10.40819</v>
+        <v>13.45458</v>
       </c>
       <c r="N64">
-        <v>34.68873</v>
+        <v>21.77339</v>
       </c>
       <c r="O64">
-        <v>25.10028</v>
+        <v>18.26749</v>
       </c>
       <c r="P64">
-        <v>33.38852</v>
+        <v>28.70218</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.25">
@@ -4338,43 +4338,43 @@
         <v>1</v>
       </c>
       <c r="D65">
-        <v>197.63</v>
+        <v>20.12</v>
       </c>
       <c r="E65">
-        <v>0.7288</v>
+        <v>-0.0497</v>
       </c>
       <c r="F65">
-        <v>1.43</v>
+        <v>-0.01</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>-0.04967709885741685</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>-0.00999999999999801</v>
       </c>
       <c r="I65">
-        <v>4.89776</v>
+        <v>7.93901</v>
       </c>
       <c r="J65">
-        <v>2.3034</v>
+        <v>-3.52444</v>
       </c>
       <c r="K65">
-        <v>3.25195</v>
+        <v>4.85189</v>
       </c>
       <c r="L65">
-        <v>13.86376</v>
+        <v>8.73941</v>
       </c>
       <c r="M65">
-        <v>34.17387</v>
+        <v>17.51574</v>
       </c>
       <c r="N65">
-        <v>53.67301</v>
+        <v>0.19522</v>
       </c>
       <c r="O65">
-        <v>45.49204</v>
+        <v>2.39401</v>
       </c>
       <c r="P65">
-        <v>77.91471</v>
+        <v>1.88586</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.25">
@@ -4388,43 +4388,43 @@
         <v>1</v>
       </c>
       <c r="D66">
-        <v>84.7065</v>
+        <v>55.055</v>
       </c>
       <c r="E66">
-        <v>0.7263</v>
+        <v>-0.0635</v>
       </c>
       <c r="F66">
-        <v>0.6108</v>
+        <v>-0.035</v>
       </c>
       <c r="G66">
-        <v>-0.0005902699894792362</v>
+        <v>-0.06353240152478434</v>
       </c>
       <c r="H66">
-        <v>-0.0004999999999881766</v>
+        <v>-0.035000000000003695</v>
       </c>
       <c r="I66">
-        <v>4.10858</v>
+        <v>8.19132</v>
       </c>
       <c r="J66">
-        <v>2.26946</v>
+        <v>2.93016</v>
       </c>
       <c r="K66">
-        <v>3.7635</v>
+        <v>2.94551</v>
       </c>
       <c r="L66">
-        <v>4.11219</v>
+        <v>13.57228</v>
       </c>
       <c r="M66">
-        <v>12.54557</v>
+        <v>43.46074</v>
       </c>
       <c r="N66">
-        <v>16.30922</v>
+        <v>32.69426</v>
       </c>
       <c r="O66">
-        <v>14.39005</v>
+        <v>34.87572</v>
       </c>
       <c r="P66">
-        <v>24.6477</v>
+        <v>38.59498</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.25">
@@ -4438,43 +4438,43 @@
         <v>1</v>
       </c>
       <c r="D67">
-        <v>160.0289</v>
+        <v>83.26</v>
       </c>
       <c r="E67">
-        <v>0.7192</v>
+        <v>-0.072</v>
       </c>
       <c r="F67">
-        <v>1.1427</v>
+        <v>-0.06</v>
       </c>
       <c r="G67">
-        <v>-0.00006248867392992498</v>
+        <v>-0.07201152184348064</v>
       </c>
       <c r="H67">
-        <v>-0.00010000000000331966</v>
+        <v>-0.05999999999998806</v>
       </c>
       <c r="I67">
-        <v>5.13064</v>
+        <v>2.80039</v>
       </c>
       <c r="J67">
-        <v>3.53196</v>
+        <v>4.47593</v>
       </c>
       <c r="K67">
-        <v>4.25483</v>
+        <v>10.54578</v>
       </c>
       <c r="L67">
-        <v>9.61676</v>
+        <v>12.31558</v>
       </c>
       <c r="M67">
-        <v>21.45063</v>
+        <v>14.55784</v>
       </c>
       <c r="N67">
-        <v>23.13249</v>
+        <v>24.88287</v>
       </c>
       <c r="O67">
-        <v>21.15186</v>
+        <v>20.51168</v>
       </c>
       <c r="P67">
-        <v>30.17811</v>
+        <v>32.64032</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.25">
@@ -4488,43 +4488,43 @@
         <v>1</v>
       </c>
       <c r="D68">
-        <v>57.91</v>
+        <v>49.74</v>
       </c>
       <c r="E68">
-        <v>0.713</v>
+        <v>-0.0804</v>
       </c>
       <c r="F68">
-        <v>0.41</v>
+        <v>-0.04</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>-0.08035355564483557</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>-0.03999999999999915</v>
       </c>
       <c r="I68">
-        <v>3.23264</v>
+        <v>2.64026</v>
       </c>
       <c r="J68">
-        <v>1.74891</v>
+        <v>3.45114</v>
       </c>
       <c r="K68">
-        <v>8.5421</v>
+        <v>6.70244</v>
       </c>
       <c r="L68">
-        <v>8.23029</v>
+        <v>11.14145</v>
       </c>
       <c r="M68">
-        <v>16.55146</v>
+        <v>14.58024</v>
       </c>
       <c r="N68">
-        <v>26.82117</v>
+        <v>23.80694</v>
       </c>
       <c r="O68">
-        <v>24.53492</v>
+        <v>19.57623</v>
       </c>
       <c r="P68">
-        <v>36.18742</v>
+        <v>33.08608</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.25">
@@ -4538,43 +4538,43 @@
         <v>1</v>
       </c>
       <c r="D69">
-        <v>73.14</v>
+        <v>73.08083</v>
       </c>
       <c r="E69">
-        <v>0.7065</v>
+        <v>-0.0809</v>
       </c>
       <c r="F69">
-        <v>0.5131</v>
+        <v>-0.05917</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>-0.0808996445173566</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>-0.059169999999994616</v>
       </c>
       <c r="I69">
-        <v>4.03418</v>
+        <v>4.57454</v>
       </c>
       <c r="J69">
-        <v>2.07967</v>
+        <v>3.59782</v>
       </c>
       <c r="K69">
-        <v>3.03903</v>
+        <v>3.80326</v>
       </c>
       <c r="L69">
-        <v>4.74481</v>
+        <v>6.22195</v>
       </c>
       <c r="M69">
-        <v>14.98393</v>
+        <v>15.83675</v>
       </c>
       <c r="N69">
-        <v>20.31104</v>
+        <v>21.58739</v>
       </c>
       <c r="O69">
-        <v>17.24648</v>
+        <v>18.11608</v>
       </c>
       <c r="P69">
-        <v>32.7337</v>
+        <v>33.18068</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.25">
@@ -4588,43 +4588,43 @@
         <v>1</v>
       </c>
       <c r="D70">
-        <v>76.14</v>
+        <v>362.14</v>
       </c>
       <c r="E70">
-        <v>0.701</v>
+        <v>-0.0855</v>
       </c>
       <c r="F70">
-        <v>0.53</v>
+        <v>-0.31</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>-0.08552903848806795</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>-0.3100000000000023</v>
       </c>
       <c r="I70">
-        <v>16.43315</v>
+        <v>7.63066</v>
       </c>
       <c r="J70">
-        <v>7.07978</v>
+        <v>1.08742</v>
       </c>
       <c r="K70">
-        <v>19.40683</v>
+        <v>2.71645</v>
       </c>
       <c r="L70">
-        <v>30.44098</v>
+        <v>10.30167</v>
       </c>
       <c r="M70">
-        <v>29.61599</v>
+        <v>34.49362</v>
       </c>
       <c r="N70">
-        <v>39.5867</v>
+        <v>29.96426</v>
       </c>
       <c r="O70">
-        <v>34.90365</v>
+        <v>30.64212</v>
       </c>
       <c r="P70">
-        <v>68.24662</v>
+        <v>50.52018</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.25">
@@ -4638,43 +4638,43 @@
         <v>1</v>
       </c>
       <c r="D71">
-        <v>123.02</v>
+        <v>69.36</v>
       </c>
       <c r="E71">
-        <v>0.6958</v>
+        <v>-0.0864</v>
       </c>
       <c r="F71">
-        <v>0.85</v>
+        <v>-0.06</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>-0.08643042350907847</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>-0.060000000000002274</v>
       </c>
       <c r="I71">
-        <v>9.36506</v>
+        <v>5.81318</v>
       </c>
       <c r="J71">
-        <v>4.20033</v>
+        <v>3.58528</v>
       </c>
       <c r="K71">
-        <v>5.09721</v>
+        <v>11.70159</v>
       </c>
       <c r="L71">
-        <v>7.65</v>
+        <v>17.40423</v>
       </c>
       <c r="M71">
-        <v>19.74856</v>
+        <v>13.7463</v>
       </c>
       <c r="N71">
-        <v>14.76298</v>
+        <v>27.99146</v>
       </c>
       <c r="O71">
-        <v>14.93498</v>
+        <v>22.83156</v>
       </c>
       <c r="P71">
-        <v>25.62489</v>
+        <v>44.74206</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.25">
@@ -4688,43 +4688,43 @@
         <v>1</v>
       </c>
       <c r="D72">
-        <v>123.05</v>
+        <v>187.79</v>
       </c>
       <c r="E72">
-        <v>0.6709</v>
+        <v>-0.0958</v>
       </c>
       <c r="F72">
-        <v>0.82</v>
+        <v>-0.18</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>-0.10107995956801497</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>-0.18999999999999773</v>
       </c>
       <c r="I72">
-        <v>2.48114</v>
+        <v>7.26193</v>
       </c>
       <c r="J72">
-        <v>-1.32365</v>
+        <v>4.89855</v>
       </c>
       <c r="K72">
-        <v>8.19472</v>
+        <v>4.42714</v>
       </c>
       <c r="L72">
-        <v>6.90005</v>
+        <v>10.93896</v>
       </c>
       <c r="M72">
-        <v>21.39444</v>
+        <v>33.54607</v>
       </c>
       <c r="N72">
-        <v>33.19172</v>
+        <v>31.00753</v>
       </c>
       <c r="O72">
-        <v>27.39655</v>
+        <v>30.91491</v>
       </c>
       <c r="P72">
-        <v>50.96852</v>
+        <v>43.57188</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.25">
@@ -4738,43 +4738,43 @@
         <v>1</v>
       </c>
       <c r="D73">
-        <v>84.9149</v>
+        <v>52.35</v>
       </c>
       <c r="E73">
-        <v>0.6709</v>
+        <v>-0.124</v>
       </c>
       <c r="F73">
-        <v>0.5659</v>
+        <v>-0.065</v>
       </c>
       <c r="G73">
-        <v>-0.00011776482365108595</v>
+        <v>-0.1335368180083943</v>
       </c>
       <c r="H73">
-        <v>-0.00010000000000331966</v>
+        <v>-0.07000000000000028</v>
       </c>
       <c r="I73">
-        <v>6.27946</v>
+        <v>1.83356</v>
       </c>
       <c r="J73">
-        <v>3.5769</v>
+        <v>1.59186</v>
       </c>
       <c r="K73">
-        <v>4.44029</v>
+        <v>1.18054</v>
       </c>
       <c r="L73">
-        <v>6.04258</v>
+        <v>-0.55293</v>
       </c>
       <c r="M73">
-        <v>14.96975</v>
+        <v>6.97983</v>
       </c>
       <c r="N73">
-        <v>14.57873</v>
+        <v>13.25683</v>
       </c>
       <c r="O73">
-        <v>14.18547</v>
+        <v>12.38245</v>
       </c>
       <c r="P73">
-        <v>23.71989</v>
+        <v>21.85598</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.25">
@@ -4788,43 +4788,43 @@
         <v>1</v>
       </c>
       <c r="D74">
-        <v>134.12</v>
+        <v>60.4</v>
       </c>
       <c r="E74">
-        <v>0.6303</v>
+        <v>-0.124</v>
       </c>
       <c r="F74">
-        <v>0.84</v>
+        <v>-0.075</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>-0.11575988093269438</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>-0.07000000000000028</v>
       </c>
       <c r="I74">
-        <v>0.01501</v>
+        <v>2.83761</v>
       </c>
       <c r="J74">
-        <v>-5.94213</v>
+        <v>2.46977</v>
       </c>
       <c r="K74">
-        <v>-2.09359</v>
+        <v>3.34667</v>
       </c>
       <c r="L74">
-        <v>-0.82595</v>
+        <v>-0.01587</v>
       </c>
       <c r="M74">
-        <v>18.00956</v>
+        <v>5.51934</v>
       </c>
       <c r="N74">
-        <v>40.95849</v>
+        <v>12.94098</v>
       </c>
       <c r="O74">
-        <v>33.69445</v>
+        <v>12.28642</v>
       </c>
       <c r="P74">
-        <v>56.41867</v>
+        <v>21.72208</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.25">
@@ -4838,43 +4838,43 @@
         <v>1</v>
       </c>
       <c r="D75">
-        <v>138.6</v>
+        <v>149.55</v>
       </c>
       <c r="E75">
-        <v>0.6244</v>
+        <v>-0.1402</v>
       </c>
       <c r="F75">
-        <v>0.86</v>
+        <v>-0.21</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>-0.09352662168480617</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>-0.13999999999998636</v>
       </c>
       <c r="I75">
-        <v>9.94532</v>
+        <v>4.15913</v>
       </c>
       <c r="J75">
-        <v>-1.86037</v>
+        <v>0.20743</v>
       </c>
       <c r="K75">
-        <v>-1.13304</v>
+        <v>3.9989</v>
       </c>
       <c r="L75">
-        <v>-0.90708</v>
+        <v>7.67208</v>
       </c>
       <c r="M75">
-        <v>15.31876</v>
+        <v>25.4443</v>
       </c>
       <c r="N75">
-        <v>16.11013</v>
+        <v>27.22276</v>
       </c>
       <c r="O75">
-        <v>19.21292</v>
+        <v>26.05407</v>
       </c>
       <c r="P75">
-        <v>24.2161</v>
+        <v>29.8104</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.25">
@@ -4888,43 +4888,43 @@
         <v>1</v>
       </c>
       <c r="D76">
-        <v>773.26</v>
+        <v>159.59</v>
       </c>
       <c r="E76">
-        <v>0.6115</v>
+        <v>-0.1814</v>
       </c>
       <c r="F76">
-        <v>4.7</v>
+        <v>-0.29</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>-0.06887914840324685</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>-0.10999999999998522</v>
       </c>
       <c r="I76">
-        <v>3.67053</v>
+        <v>4.24171</v>
       </c>
       <c r="J76">
-        <v>2.33484</v>
+        <v>1.57701</v>
       </c>
       <c r="K76">
-        <v>4.54476</v>
+        <v>3.62634</v>
       </c>
       <c r="L76">
-        <v>4.95475</v>
+        <v>5.48072</v>
       </c>
       <c r="M76">
-        <v>11.81484</v>
+        <v>19.20006</v>
       </c>
       <c r="N76">
-        <v>15.67135</v>
+        <v>25.87864</v>
       </c>
       <c r="O76">
-        <v>13.32697</v>
+        <v>25.70035</v>
       </c>
       <c r="P76">
-        <v>22.84062</v>
+        <v>34.02131</v>
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
@@ -4938,43 +4938,43 @@
         <v>1</v>
       </c>
       <c r="D77">
-        <v>710.71</v>
+        <v>191.32</v>
       </c>
       <c r="E77">
-        <v>0.6101</v>
+        <v>-0.193</v>
       </c>
       <c r="F77">
-        <v>4.31</v>
+        <v>-0.37</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>-0.19301998017632874</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>-0.37000000000000455</v>
       </c>
       <c r="I77">
-        <v>3.67463</v>
+        <v>4.50603</v>
       </c>
       <c r="J77">
-        <v>2.34098</v>
+        <v>1.09235</v>
       </c>
       <c r="K77">
-        <v>4.55983</v>
+        <v>4.73819</v>
       </c>
       <c r="L77">
-        <v>4.97189</v>
+        <v>5.98355</v>
       </c>
       <c r="M77">
-        <v>11.84246</v>
+        <v>13.82937</v>
       </c>
       <c r="N77">
-        <v>15.72213</v>
+        <v>19.5061</v>
       </c>
       <c r="O77">
-        <v>13.36219</v>
+        <v>18.47316</v>
       </c>
       <c r="P77">
-        <v>22.92953</v>
+        <v>27.70874</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.25">
@@ -4988,43 +4988,43 @@
         <v>1</v>
       </c>
       <c r="D78">
-        <v>68.29</v>
+        <v>59.77</v>
       </c>
       <c r="E78">
-        <v>0.604</v>
+        <v>-0.2004</v>
       </c>
       <c r="F78">
-        <v>0.41</v>
+        <v>-0.12</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>-0.20036734012355556</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>-0.11999999999999744</v>
       </c>
       <c r="I78">
-        <v>1.99965</v>
+        <v>3.7655</v>
       </c>
       <c r="J78">
-        <v>1.61127</v>
+        <v>3.67401</v>
       </c>
       <c r="K78">
-        <v>3.57266</v>
+        <v>6.22212</v>
       </c>
       <c r="L78">
-        <v>5.99003</v>
+        <v>9.7541</v>
       </c>
       <c r="M78">
-        <v>11.67942</v>
+        <v>15.92433</v>
       </c>
       <c r="N78">
-        <v>20.25646</v>
+        <v>27.31651</v>
       </c>
       <c r="O78">
-        <v>18.32716</v>
+        <v>22.96274</v>
       </c>
       <c r="P78">
-        <v>27.29925</v>
+        <v>36.63657</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.25">
@@ -5038,43 +5038,43 @@
         <v>1</v>
       </c>
       <c r="D79">
-        <v>60.2557</v>
+        <v>122.785</v>
       </c>
       <c r="E79">
-        <v>0.5742</v>
+        <v>-0.2154</v>
       </c>
       <c r="F79">
-        <v>0.344</v>
+        <v>-0.265</v>
       </c>
       <c r="G79">
-        <v>-0.0004978757302224733</v>
+        <v>-0.2153596099146693</v>
       </c>
       <c r="H79">
-        <v>-0.00030000000000285354</v>
+        <v>-0.26500000000000057</v>
       </c>
       <c r="I79">
-        <v>4.1261</v>
+        <v>3.76181</v>
       </c>
       <c r="J79">
-        <v>-0.0992</v>
+        <v>0.57227</v>
       </c>
       <c r="K79">
-        <v>4.0621</v>
+        <v>8.86729</v>
       </c>
       <c r="L79">
-        <v>5.99232</v>
+        <v>9.32151</v>
       </c>
       <c r="M79">
-        <v>17.49034</v>
+        <v>22.14906</v>
       </c>
       <c r="N79">
-        <v>23.43446</v>
+        <v>33.52562</v>
       </c>
       <c r="O79">
-        <v>21.09089</v>
+        <v>28.18848</v>
       </c>
       <c r="P79">
-        <v>38.01504</v>
+        <v>52.16953</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
@@ -5088,43 +5088,43 @@
         <v>1</v>
       </c>
       <c r="D80">
-        <v>100.02</v>
+        <v>75.93</v>
       </c>
       <c r="E80">
-        <v>0.5732</v>
+        <v>-0.2496</v>
       </c>
       <c r="F80">
-        <v>0.57</v>
+        <v>-0.19</v>
       </c>
       <c r="G80">
-        <v>0</v>
+        <v>-0.27580772261622505</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>-0.20999999999999375</v>
       </c>
       <c r="I80">
-        <v>4.49458</v>
+        <v>8.74016</v>
       </c>
       <c r="J80">
-        <v>3.61582</v>
+        <v>4.96691</v>
       </c>
       <c r="K80">
-        <v>3.82466</v>
+        <v>17.20064</v>
       </c>
       <c r="L80">
-        <v>6.01396</v>
+        <v>25.8709</v>
       </c>
       <c r="M80">
-        <v>9.46246</v>
+        <v>18.54025</v>
       </c>
       <c r="N80">
-        <v>13.40814</v>
+        <v>40.05366</v>
       </c>
       <c r="O80">
-        <v>11.80375</v>
+        <v>32.41113</v>
       </c>
       <c r="P80">
-        <v>18.16157</v>
+        <v>66.87196</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
@@ -5138,43 +5138,43 @@
         <v>1</v>
       </c>
       <c r="D81">
-        <v>63.3</v>
+        <v>97.36</v>
       </c>
       <c r="E81">
-        <v>0.556</v>
+        <v>-0.251</v>
       </c>
       <c r="F81">
-        <v>0.35</v>
+        <v>-0.245</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>-0.24590163934425707</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>-0.23999999999999488</v>
       </c>
       <c r="I81">
-        <v>7.37076</v>
+        <v>0.59983</v>
       </c>
       <c r="J81">
-        <v>3.50329</v>
+        <v>-0.26201</v>
       </c>
       <c r="K81">
-        <v>1.36745</v>
+        <v>0.06363</v>
       </c>
       <c r="L81">
-        <v>2.75514</v>
+        <v>-0.32909</v>
       </c>
       <c r="M81">
-        <v>10.20427</v>
+        <v>-0.49376</v>
       </c>
       <c r="N81">
-        <v>6.50005</v>
+        <v>0.34354</v>
       </c>
       <c r="O81">
-        <v>6.55992</v>
+        <v>-0.01016</v>
       </c>
       <c r="P81">
-        <v>18.62636</v>
+        <v>2.44421</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
@@ -5188,43 +5188,43 @@
         <v>1</v>
       </c>
       <c r="D82">
-        <v>43.96</v>
+        <v>70.41</v>
       </c>
       <c r="E82">
-        <v>0.5489</v>
+        <v>-0.2691</v>
       </c>
       <c r="F82">
-        <v>0.24</v>
+        <v>-0.19</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>-0.2691218130311583</v>
       </c>
       <c r="H82">
-        <v>0</v>
+        <v>-0.18999999999999773</v>
       </c>
       <c r="I82">
-        <v>5.41331</v>
+        <v>7.60335</v>
       </c>
       <c r="J82">
-        <v>4.54202</v>
+        <v>3.49826</v>
       </c>
       <c r="K82">
-        <v>6.14979</v>
+        <v>1.62872</v>
       </c>
       <c r="L82">
-        <v>8.36727</v>
+        <v>5.33755</v>
       </c>
       <c r="M82">
-        <v>16.14786</v>
+        <v>12.68118</v>
       </c>
       <c r="N82">
-        <v>16.69598</v>
+        <v>14.65013</v>
       </c>
       <c r="O82">
-        <v>15.20452</v>
+        <v>18.72902</v>
       </c>
       <c r="P82">
-        <v>26.84659</v>
+        <v>29.67144</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
@@ -5238,43 +5238,43 @@
         <v>1</v>
       </c>
       <c r="D83">
-        <v>51.3</v>
+        <v>93.05</v>
       </c>
       <c r="E83">
-        <v>0.5488</v>
+        <v>-0.2744</v>
       </c>
       <c r="F83">
-        <v>0.28</v>
+        <v>-0.256</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>-0.27864108884364497</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>-0.2600000000000051</v>
       </c>
       <c r="I83">
-        <v>5.51653</v>
+        <v>2.96233</v>
       </c>
       <c r="J83">
-        <v>4.30964</v>
+        <v>4.29261</v>
       </c>
       <c r="K83">
-        <v>7.07013</v>
+        <v>7.27732</v>
       </c>
       <c r="L83">
-        <v>9.87205</v>
+        <v>6.44025</v>
       </c>
       <c r="M83">
-        <v>15.66492</v>
+        <v>7.67273</v>
       </c>
       <c r="N83">
-        <v>21.16562</v>
+        <v>19.81936</v>
       </c>
       <c r="O83">
-        <v>17.7602</v>
+        <v>14.75686</v>
       </c>
       <c r="P83">
-        <v>27.80198</v>
+        <v>25.31136</v>
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
@@ -5288,43 +5288,43 @@
         <v>1</v>
       </c>
       <c r="D84">
-        <v>69.51</v>
+        <v>72.57566</v>
       </c>
       <c r="E84">
-        <v>0.5367</v>
+        <v>-0.2808</v>
       </c>
       <c r="F84">
-        <v>0.3711</v>
+        <v>-0.20434</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>-0.28167078867820594</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>-0.2049999999999983</v>
       </c>
       <c r="I84">
-        <v>2.32249</v>
+        <v>8.69912</v>
       </c>
       <c r="J84">
-        <v>4.06198</v>
+        <v>3.76433</v>
       </c>
       <c r="K84">
-        <v>7.11444</v>
+        <v>2.70659</v>
       </c>
       <c r="L84">
-        <v>9.41144</v>
+        <v>9.74806</v>
       </c>
       <c r="M84">
-        <v>16.99358</v>
+        <v>43.69216</v>
       </c>
       <c r="N84">
-        <v>25.11633</v>
+        <v>51.10041</v>
       </c>
       <c r="O84">
-        <v>21.88708</v>
+        <v>51.04671</v>
       </c>
       <c r="P84">
-        <v>35.86437</v>
+        <v>71.0317</v>
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
@@ -5338,43 +5338,43 @@
         <v>1</v>
       </c>
       <c r="D85">
-        <v>69.42</v>
+        <v>21.965</v>
       </c>
       <c r="E85">
-        <v>0.5358</v>
+        <v>-0.2951</v>
       </c>
       <c r="F85">
-        <v>0.37</v>
+        <v>-0.065</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>-0.29505220154335576</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>-0.06500000000000128</v>
       </c>
       <c r="I85">
-        <v>10.76236</v>
+        <v>0.85939</v>
       </c>
       <c r="J85">
-        <v>4.97168</v>
+        <v>-0.23546</v>
       </c>
       <c r="K85">
-        <v>13.08022</v>
+        <v>0.27463</v>
       </c>
       <c r="L85">
-        <v>20.23674</v>
+        <v>-0.28198</v>
       </c>
       <c r="M85">
-        <v>20.79011</v>
+        <v>-0.29113</v>
       </c>
       <c r="N85">
-        <v>27.70996</v>
+        <v>0.98155</v>
       </c>
       <c r="O85">
-        <v>24.34756</v>
+        <v>0.45231</v>
       </c>
       <c r="P85">
-        <v>45.52905</v>
+        <v>3.89937</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.25">
@@ -5388,43 +5388,43 @@
         <v>1</v>
       </c>
       <c r="D86">
-        <v>47.01</v>
+        <v>121.07</v>
       </c>
       <c r="E86">
-        <v>0.5346</v>
+        <v>-0.2965</v>
       </c>
       <c r="F86">
-        <v>0.25</v>
+        <v>-0.36</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>-0.35405516673528764</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>-0.4300000000000068</v>
       </c>
       <c r="I86">
-        <v>7.78762</v>
+        <v>7.31707</v>
       </c>
       <c r="J86">
-        <v>6.55075</v>
+        <v>6.43295</v>
       </c>
       <c r="K86">
-        <v>17.01811</v>
+        <v>5.47929</v>
       </c>
       <c r="L86">
-        <v>14.69596</v>
+        <v>11.01714</v>
       </c>
       <c r="M86">
-        <v>8.78022</v>
+        <v>31.59587</v>
       </c>
       <c r="N86">
-        <v>8.57721</v>
+        <v>28.06307</v>
       </c>
       <c r="O86">
-        <v>12.32479</v>
+        <v>29.21389</v>
       </c>
       <c r="P86">
-        <v>12.05916</v>
+        <v>40.86759</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
@@ -5438,43 +5438,43 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>33.8622</v>
+        <v>47.7901</v>
       </c>
       <c r="E87">
-        <v>0.5111</v>
+        <v>-0.4116</v>
       </c>
       <c r="F87">
-        <v>0.1722</v>
+        <v>-0.1975</v>
       </c>
       <c r="G87">
-        <v>0.0005906325674783943</v>
+        <v>-0.4123947653580001</v>
       </c>
       <c r="H87">
-        <v>0.00019999999999953388</v>
+        <v>-0.19789999999999708</v>
       </c>
       <c r="I87">
-        <v>1.23234</v>
+        <v>3.76937</v>
       </c>
       <c r="J87">
-        <v>4.69381</v>
+        <v>-2.77736</v>
       </c>
       <c r="K87">
-        <v>7.02256</v>
+        <v>-0.0148</v>
       </c>
       <c r="L87">
-        <v>9.74259</v>
+        <v>0.70435</v>
       </c>
       <c r="M87">
-        <v>14.1308</v>
+        <v>12.56573</v>
       </c>
       <c r="N87">
-        <v>23.47518</v>
+        <v>23.1548</v>
       </c>
       <c r="O87">
-        <v>19.26346</v>
+        <v>21.66131</v>
       </c>
       <c r="P87">
-        <v>28.88792</v>
+        <v>26.0912</v>
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.25">
@@ -5488,43 +5488,43 @@
         <v>1</v>
       </c>
       <c r="D88">
-        <v>55.92</v>
+        <v>151.875</v>
       </c>
       <c r="E88">
-        <v>0.4852</v>
+        <v>-0.4164</v>
       </c>
       <c r="F88">
-        <v>0.27</v>
+        <v>-0.635</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>-0.41636613992524485</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>-0.6349999999999909</v>
       </c>
       <c r="I88">
-        <v>2.66888</v>
+        <v>4.45344</v>
       </c>
       <c r="J88">
-        <v>2.74452</v>
+        <v>3.11611</v>
       </c>
       <c r="K88">
-        <v>5.54845</v>
+        <v>0.18339</v>
       </c>
       <c r="L88">
-        <v>7.49479</v>
+        <v>8.31539</v>
       </c>
       <c r="M88">
-        <v>14.35051</v>
+        <v>32.61827</v>
       </c>
       <c r="N88">
-        <v>23.66909</v>
+        <v>44.47072</v>
       </c>
       <c r="O88">
-        <v>19.76211</v>
+        <v>41.819</v>
       </c>
       <c r="P88">
-        <v>33.31802</v>
+        <v>57.32633</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.25">
@@ -5538,43 +5538,43 @@
         <v>1</v>
       </c>
       <c r="D89">
-        <v>66.5598</v>
+        <v>51.43</v>
       </c>
       <c r="E89">
-        <v>0.4828</v>
+        <v>-0.4259</v>
       </c>
       <c r="F89">
-        <v>0.3198</v>
+        <v>-0.22</v>
       </c>
       <c r="G89">
-        <v>-0.0003004807692407441</v>
+        <v>-0.4259438528557577</v>
       </c>
       <c r="H89">
-        <v>-0.0002000000000066393</v>
+        <v>-0.21999999999999886</v>
       </c>
       <c r="I89">
-        <v>3.06929</v>
+        <v>2.13726</v>
       </c>
       <c r="J89">
-        <v>1.06399</v>
+        <v>2.28436</v>
       </c>
       <c r="K89">
-        <v>3.75054</v>
+        <v>3.67148</v>
       </c>
       <c r="L89">
-        <v>6.11039</v>
+        <v>3.54804</v>
       </c>
       <c r="M89">
-        <v>12.61808</v>
+        <v>9.90102</v>
       </c>
       <c r="N89">
-        <v>21.09659</v>
+        <v>23.23041</v>
       </c>
       <c r="O89">
-        <v>18.43114</v>
+        <v>17.10105</v>
       </c>
       <c r="P89">
-        <v>26.3257</v>
+        <v>29.71447</v>
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.25">
@@ -5588,43 +5588,43 @@
         <v>1</v>
       </c>
       <c r="D90">
-        <v>63.14</v>
+        <v>122.92</v>
       </c>
       <c r="E90">
-        <v>0.4774</v>
+        <v>-0.4374</v>
       </c>
       <c r="F90">
-        <v>0.3</v>
+        <v>-0.54</v>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>-0.5018617451837498</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>-0.6200000000000045</v>
       </c>
       <c r="I90">
-        <v>1.31892</v>
+        <v>5.50239</v>
       </c>
       <c r="J90">
-        <v>2.1679</v>
+        <v>0.51282</v>
       </c>
       <c r="K90">
-        <v>4.3128</v>
+        <v>-3.48601</v>
       </c>
       <c r="L90">
-        <v>5.55284</v>
+        <v>-4.26423</v>
       </c>
       <c r="M90">
-        <v>8.2647</v>
+        <v>4.31919</v>
       </c>
       <c r="N90">
-        <v>14.41492</v>
+        <v>27.04518</v>
       </c>
       <c r="O90">
-        <v>11.87467</v>
+        <v>25.73079</v>
       </c>
       <c r="P90">
-        <v>22.07804</v>
+        <v>39.89147</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.25">
@@ -5638,43 +5638,43 @@
         <v>1</v>
       </c>
       <c r="D91">
-        <v>31.575</v>
+        <v>35.96</v>
       </c>
       <c r="E91">
-        <v>0.4613</v>
+        <v>-0.443</v>
       </c>
       <c r="F91">
-        <v>0.145</v>
+        <v>-0.16</v>
       </c>
       <c r="G91">
-        <v>0</v>
+        <v>-0.36021058464949446</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>-0.13000000000000256</v>
       </c>
       <c r="I91">
-        <v>2.27347</v>
+        <v>4.09458</v>
       </c>
       <c r="J91">
-        <v>2.87488</v>
+        <v>1.63288</v>
       </c>
       <c r="K91">
-        <v>5.45518</v>
+        <v>3.98522</v>
       </c>
       <c r="L91">
-        <v>7.13531</v>
+        <v>5.50016</v>
       </c>
       <c r="M91">
-        <v>13.38954</v>
+        <v>11.19836</v>
       </c>
       <c r="N91">
-        <v>23.2344</v>
+        <v>23.69866</v>
       </c>
       <c r="O91">
-        <v>19.49678</v>
+        <v>20.78251</v>
       </c>
       <c r="P91">
-        <v>32.8518</v>
+        <v>28.90558</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
@@ -5688,43 +5688,43 @@
         <v>1</v>
       </c>
       <c r="D92">
-        <v>166.82</v>
+        <v>133.52</v>
       </c>
       <c r="E92">
-        <v>0.4546</v>
+        <v>-0.4474</v>
       </c>
       <c r="F92">
-        <v>0.755</v>
+        <v>-0.6</v>
       </c>
       <c r="G92">
-        <v>0</v>
+        <v>-0.4473605726215287</v>
       </c>
       <c r="H92">
-        <v>0</v>
+        <v>-0.5999999999999943</v>
       </c>
       <c r="I92">
-        <v>2.42898</v>
+        <v>1.14553</v>
       </c>
       <c r="J92">
-        <v>1.5485</v>
+        <v>-2.16504</v>
       </c>
       <c r="K92">
-        <v>6.11098</v>
+        <v>-1.41042</v>
       </c>
       <c r="L92">
-        <v>9.57157</v>
+        <v>1.88264</v>
       </c>
       <c r="M92">
-        <v>11.90365</v>
+        <v>18.83301</v>
       </c>
       <c r="N92">
-        <v>23.57131</v>
+        <v>38.86275</v>
       </c>
       <c r="O92">
-        <v>19.1974</v>
+        <v>34.62734</v>
       </c>
       <c r="P92">
-        <v>30.31364</v>
+        <v>56.88508</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
@@ -5738,43 +5738,43 @@
         <v>1</v>
       </c>
       <c r="D93">
-        <v>72.9688</v>
+        <v>90.9</v>
       </c>
       <c r="E93">
-        <v>0.4526</v>
+        <v>-0.449</v>
       </c>
       <c r="F93">
-        <v>0.3288</v>
+        <v>-0.41</v>
       </c>
       <c r="G93">
-        <v>-0.00027408899668685124</v>
+        <v>-0.4490198225824078</v>
       </c>
       <c r="H93">
-        <v>-0.00019999999999242846</v>
+        <v>-0.4099999999999966</v>
       </c>
       <c r="I93">
-        <v>1.21069</v>
+        <v>5.30871</v>
       </c>
       <c r="J93">
-        <v>2.25309</v>
+        <v>-3.49022</v>
       </c>
       <c r="K93">
-        <v>3.88841</v>
+        <v>0.02192</v>
       </c>
       <c r="L93">
-        <v>6.4302</v>
+        <v>6.3272</v>
       </c>
       <c r="M93">
-        <v>12.73996</v>
+        <v>46</v>
       </c>
       <c r="N93">
-        <v>17.86141</v>
+        <v>55.79648</v>
       </c>
       <c r="O93">
-        <v>15.48249</v>
+        <v>53.07834</v>
       </c>
       <c r="P93">
-        <v>25.5466</v>
+        <v>81.87728</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.25">
@@ -5788,43 +5788,43 @@
         <v>1</v>
       </c>
       <c r="D94">
-        <v>77.001</v>
+        <v>210.61</v>
       </c>
       <c r="E94">
-        <v>0.435</v>
+        <v>-0.4655</v>
       </c>
       <c r="F94">
-        <v>0.3335</v>
+        <v>-0.985</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>-0.48667548667547383</v>
       </c>
       <c r="H94">
-        <v>0</v>
+        <v>-1.0299999999999727</v>
       </c>
       <c r="I94">
-        <v>3.20323</v>
+        <v>22.13447</v>
       </c>
       <c r="J94">
-        <v>1.46186</v>
+        <v>11.06649</v>
       </c>
       <c r="K94">
-        <v>4.97745</v>
+        <v>4.92263</v>
       </c>
       <c r="L94">
-        <v>4.89144</v>
+        <v>20.92355</v>
       </c>
       <c r="M94">
-        <v>9.77927</v>
+        <v>97.15654</v>
       </c>
       <c r="N94">
-        <v>17.81581</v>
+        <v>74.46784</v>
       </c>
       <c r="O94">
-        <v>14.80222</v>
+        <v>80.4741</v>
       </c>
       <c r="P94">
-        <v>25.71336</v>
+        <v>117.7164</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.25">
@@ -5838,43 +5838,43 @@
         <v>1</v>
       </c>
       <c r="D95">
-        <v>91.31</v>
+        <v>57.64</v>
       </c>
       <c r="E95">
-        <v>0.4289</v>
+        <v>-0.4834</v>
       </c>
       <c r="F95">
-        <v>0.39</v>
+        <v>-0.28</v>
       </c>
       <c r="G95">
-        <v>0</v>
+        <v>-0.4662407183560629</v>
       </c>
       <c r="H95">
-        <v>0</v>
+        <v>-0.269999999999996</v>
       </c>
       <c r="I95">
-        <v>13.32595</v>
+        <v>2.4354</v>
       </c>
       <c r="J95">
-        <v>-3.24614</v>
+        <v>2.47379</v>
       </c>
       <c r="K95">
-        <v>0.95363</v>
+        <v>8.51793</v>
       </c>
       <c r="L95">
-        <v>11.20502</v>
+        <v>8.56363</v>
       </c>
       <c r="M95">
-        <v>52.58449</v>
+        <v>13.41488</v>
       </c>
       <c r="N95">
-        <v>53.11721</v>
+        <v>27.49811</v>
       </c>
       <c r="O95">
-        <v>54.50428</v>
+        <v>24.50719</v>
       </c>
       <c r="P95">
-        <v>83.57148</v>
+        <v>36.47938</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.25">
@@ -5888,43 +5888,43 @@
         <v>1</v>
       </c>
       <c r="D96">
-        <v>247.81</v>
+        <v>69.23</v>
       </c>
       <c r="E96">
-        <v>0.4266</v>
+        <v>-0.5003</v>
       </c>
       <c r="F96">
-        <v>1.0527</v>
+        <v>-0.3481</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>-0.5001580959498677</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>-0.347999999999999</v>
       </c>
       <c r="I96">
-        <v>2.6195</v>
+        <v>5.23051</v>
       </c>
       <c r="J96">
-        <v>3.18096</v>
+        <v>3.90491</v>
       </c>
       <c r="K96">
-        <v>5.4066</v>
+        <v>6.17666</v>
       </c>
       <c r="L96">
-        <v>7.32009</v>
+        <v>7.52246</v>
       </c>
       <c r="M96">
-        <v>12.8108</v>
+        <v>19.26043</v>
       </c>
       <c r="N96">
-        <v>22.31853</v>
+        <v>22.59423</v>
       </c>
       <c r="O96">
-        <v>18.66084</v>
+        <v>21.27036</v>
       </c>
       <c r="P96">
-        <v>30.66924</v>
+        <v>26.51763</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.25">
@@ -5938,43 +5938,43 @@
         <v>1</v>
       </c>
       <c r="D97">
-        <v>41.6881</v>
+        <v>37.42</v>
       </c>
       <c r="E97">
-        <v>0.4078</v>
+        <v>-0.5052</v>
       </c>
       <c r="F97">
-        <v>0.1693</v>
+        <v>-0.19</v>
       </c>
       <c r="G97">
-        <v>0.00023987718287328303</v>
+        <v>-0.5051847912789091</v>
       </c>
       <c r="H97">
-        <v>0.00009999999999621423</v>
+        <v>-0.18999999999999773</v>
       </c>
       <c r="I97">
-        <v>1.2686</v>
+        <v>4.71248</v>
       </c>
       <c r="J97">
-        <v>4.19177</v>
+        <v>1.49538</v>
       </c>
       <c r="K97">
-        <v>6.37455</v>
+        <v>-3.8654</v>
       </c>
       <c r="L97">
-        <v>9.10782</v>
+        <v>-7.0938</v>
       </c>
       <c r="M97">
-        <v>10.49887</v>
+        <v>1.35222</v>
       </c>
       <c r="N97">
-        <v>24.28189</v>
+        <v>4.39674</v>
       </c>
       <c r="O97">
-        <v>16.59301</v>
+        <v>3.11511</v>
       </c>
       <c r="P97">
-        <v>39.587</v>
+        <v>12.4393</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.25">
@@ -5988,43 +5988,43 @@
         <v>1</v>
       </c>
       <c r="D98">
-        <v>32.31</v>
+        <v>63.87</v>
       </c>
       <c r="E98">
-        <v>0.404</v>
+        <v>-0.514</v>
       </c>
       <c r="F98">
-        <v>0.13</v>
+        <v>-0.33</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>-0.5295950155763293</v>
       </c>
       <c r="H98">
-        <v>0</v>
+        <v>-0.3400000000000034</v>
       </c>
       <c r="I98">
-        <v>2.2194</v>
+        <v>2.67028</v>
       </c>
       <c r="J98">
-        <v>3.00319</v>
+        <v>3.80802</v>
       </c>
       <c r="K98">
-        <v>5.34934</v>
+        <v>6.74134</v>
       </c>
       <c r="L98">
-        <v>7.23432</v>
+        <v>9.27056</v>
       </c>
       <c r="M98">
-        <v>13.49179</v>
+        <v>9.55731</v>
       </c>
       <c r="N98">
-        <v>23.1614</v>
+        <v>18.17387</v>
       </c>
       <c r="O98">
-        <v>19.41455</v>
+        <v>15.1691</v>
       </c>
       <c r="P98">
-        <v>33.06284</v>
+        <v>22.95601</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.25">
@@ -6038,43 +6038,43 @@
         <v>1</v>
       </c>
       <c r="D99">
-        <v>149.69</v>
+        <v>147.08</v>
       </c>
       <c r="E99">
-        <v>0.3957</v>
+        <v>-0.5544</v>
       </c>
       <c r="F99">
-        <v>0.59</v>
+        <v>-0.82</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>-0.5544286680189271</v>
       </c>
       <c r="H99">
-        <v>0</v>
+        <v>-0.8199999999999932</v>
       </c>
       <c r="I99">
-        <v>10.21202</v>
+        <v>5.81462</v>
       </c>
       <c r="J99">
-        <v>-0.444</v>
+        <v>1.43288</v>
       </c>
       <c r="K99">
-        <v>4.32528</v>
+        <v>3.51518</v>
       </c>
       <c r="L99">
-        <v>9.14612</v>
+        <v>6.78361</v>
       </c>
       <c r="M99">
-        <v>30.02392</v>
+        <v>20.48431</v>
       </c>
       <c r="N99">
-        <v>26.30051</v>
+        <v>32.23728</v>
       </c>
       <c r="O99">
-        <v>26.44967</v>
+        <v>26.94545</v>
       </c>
       <c r="P99">
-        <v>32.01077</v>
+        <v>47.52272</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.25">
@@ -6088,43 +6088,43 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>159.7</v>
+        <v>152.525</v>
       </c>
       <c r="E100">
-        <v>0.3834</v>
+        <v>-0.5769</v>
       </c>
       <c r="F100">
-        <v>0.61</v>
+        <v>-0.885</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>-0.6092792910204629</v>
       </c>
       <c r="H100">
-        <v>0</v>
+        <v>-0.9350000000000023</v>
       </c>
       <c r="I100">
-        <v>10.49693</v>
+        <v>8.31505</v>
       </c>
       <c r="J100">
-        <v>1.07174</v>
+        <v>0.92131</v>
       </c>
       <c r="K100">
-        <v>4.00259</v>
+        <v>-0.47124</v>
       </c>
       <c r="L100">
-        <v>7.3955</v>
+        <v>8.60102</v>
       </c>
       <c r="M100">
-        <v>23.92363</v>
+        <v>33.34309</v>
       </c>
       <c r="N100">
-        <v>24.15395</v>
+        <v>40.14682</v>
       </c>
       <c r="O100">
-        <v>26.15675</v>
+        <v>40.43454</v>
       </c>
       <c r="P100">
-        <v>35.97964</v>
+        <v>67.38141</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.25">
@@ -6138,43 +6138,43 @@
         <v>1</v>
       </c>
       <c r="D101">
-        <v>134.12</v>
+        <v>103.39</v>
       </c>
       <c r="E101">
-        <v>0.3742</v>
+        <v>-0.591</v>
       </c>
       <c r="F101">
-        <v>0.5</v>
+        <v>-0.6147</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>-0.701114099116408</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>-0.730000000000004</v>
       </c>
       <c r="I101">
-        <v>2.24462</v>
+        <v>5.06779</v>
       </c>
       <c r="J101">
-        <v>3.38119</v>
+        <v>5.79829</v>
       </c>
       <c r="K101">
-        <v>5.78335</v>
+        <v>3.8539</v>
       </c>
       <c r="L101">
-        <v>8.7815</v>
+        <v>6.05935</v>
       </c>
       <c r="M101">
-        <v>13.24</v>
+        <v>15.65557</v>
       </c>
       <c r="N101">
-        <v>21.0253</v>
+        <v>22.29894</v>
       </c>
       <c r="O101">
-        <v>17.75971</v>
+        <v>20.92161</v>
       </c>
       <c r="P101">
-        <v>31.33383</v>
+        <v>27.40435</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.25">
@@ -6188,43 +6188,43 @@
         <v>1</v>
       </c>
       <c r="D102">
-        <v>309.32</v>
+        <v>195.06</v>
       </c>
       <c r="E102">
-        <v>0.3732</v>
+        <v>-0.6114</v>
       </c>
       <c r="F102">
-        <v>1.15</v>
+        <v>-1.2</v>
       </c>
       <c r="G102">
-        <v>0</v>
+        <v>-0.6650845869447927</v>
       </c>
       <c r="H102">
-        <v>0</v>
+        <v>-1.3060000000000116</v>
       </c>
       <c r="I102">
-        <v>9.64244</v>
+        <v>4.65761</v>
       </c>
       <c r="J102">
-        <v>-2.07667</v>
+        <v>-0.23368</v>
       </c>
       <c r="K102">
-        <v>1.25125</v>
+        <v>1.18943</v>
       </c>
       <c r="L102">
-        <v>6.61247</v>
+        <v>8.54165</v>
       </c>
       <c r="M102">
-        <v>27.25137</v>
+        <v>37.19448</v>
       </c>
       <c r="N102">
-        <v>24.52786</v>
+        <v>48.57266</v>
       </c>
       <c r="O102">
-        <v>24.13992</v>
+        <v>46.74102</v>
       </c>
       <c r="P102">
-        <v>29.44429</v>
+        <v>68.83821</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.25">
@@ -6238,43 +6238,43 @@
         <v>1</v>
       </c>
       <c r="D103">
-        <v>245.23</v>
+        <v>139.94</v>
       </c>
       <c r="E103">
-        <v>0.3519</v>
+        <v>-0.5967</v>
       </c>
       <c r="F103">
-        <v>0.86</v>
+        <v>-0.84</v>
       </c>
       <c r="G103">
-        <v>0</v>
+        <v>-0.6601831475828827</v>
       </c>
       <c r="H103">
-        <v>0</v>
+        <v>-0.9300000000000068</v>
       </c>
       <c r="I103">
-        <v>2.4782</v>
+        <v>5.97873</v>
       </c>
       <c r="J103">
-        <v>2.37946</v>
+        <v>3.55167</v>
       </c>
       <c r="K103">
-        <v>5.22173</v>
+        <v>4.27163</v>
       </c>
       <c r="L103">
-        <v>7.27291</v>
+        <v>9.7357</v>
       </c>
       <c r="M103">
-        <v>9.69658</v>
+        <v>32.73419</v>
       </c>
       <c r="N103">
-        <v>14.41436</v>
+        <v>34.93433</v>
       </c>
       <c r="O103">
-        <v>12.10722</v>
+        <v>34.11267</v>
       </c>
       <c r="P103">
-        <v>20.59218</v>
+        <v>47.30992</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.25">
@@ -6288,43 +6288,43 @@
         <v>1</v>
       </c>
       <c r="D104">
-        <v>22.03</v>
+        <v>110.25</v>
       </c>
       <c r="E104">
-        <v>0.3188</v>
+        <v>-0.6757</v>
       </c>
       <c r="F104">
-        <v>0.07</v>
+        <v>-0.75</v>
       </c>
       <c r="G104">
-        <v>0</v>
+        <v>-0.6756756756756757</v>
       </c>
       <c r="H104">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="I104">
-        <v>0.42481</v>
+        <v>2.35151</v>
       </c>
       <c r="J104">
-        <v>-0.41989</v>
+        <v>3.61069</v>
       </c>
       <c r="K104">
-        <v>0.26368</v>
+        <v>7.28757</v>
       </c>
       <c r="L104">
-        <v>0.03954</v>
+        <v>8.10261</v>
       </c>
       <c r="M104">
-        <v>-0.16396</v>
+        <v>10.65268</v>
       </c>
       <c r="N104">
-        <v>1.46798</v>
+        <v>27.29923</v>
       </c>
       <c r="O104">
-        <v>0.44134</v>
+        <v>23.01322</v>
       </c>
       <c r="P104">
-        <v>3.83648</v>
+        <v>39.39601</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.25">
@@ -6338,43 +6338,43 @@
         <v>1</v>
       </c>
       <c r="D105">
-        <v>84.0687</v>
+        <v>147.18</v>
       </c>
       <c r="E105">
-        <v>0.2899</v>
+        <v>-0.7954</v>
       </c>
       <c r="F105">
-        <v>0.243</v>
+        <v>-1.18</v>
       </c>
       <c r="G105">
-        <v>-0.0003568497305733958</v>
+        <v>-0.7953626314370495</v>
       </c>
       <c r="H105">
-        <v>-0.0002999999999957481</v>
+        <v>-1.1800000000000068</v>
       </c>
       <c r="I105">
-        <v>3.73741</v>
+        <v>14.64441</v>
       </c>
       <c r="J105">
-        <v>5.79565</v>
+        <v>8.45988</v>
       </c>
       <c r="K105">
-        <v>6.56401</v>
+        <v>5.81345</v>
       </c>
       <c r="L105">
-        <v>10.22337</v>
+        <v>17.56339</v>
       </c>
       <c r="M105">
-        <v>26.06204</v>
+        <v>65.65309</v>
       </c>
       <c r="N105">
-        <v>34.81005</v>
+        <v>55.27203</v>
       </c>
       <c r="O105">
-        <v>30.82215</v>
+        <v>57.37998</v>
       </c>
       <c r="P105">
-        <v>40.30491</v>
+        <v>82.19663</v>
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.25">
@@ -6388,43 +6388,43 @@
         <v>1</v>
       </c>
       <c r="D106">
-        <v>109.6397</v>
+        <v>85.88</v>
       </c>
       <c r="E106">
-        <v>0.1916</v>
+        <v>-0.8429</v>
       </c>
       <c r="F106">
-        <v>0.2097</v>
+        <v>-0.73</v>
       </c>
       <c r="G106">
-        <v>-0.0002736227654102044</v>
+        <v>-1.0485078926143687</v>
       </c>
       <c r="H106">
-        <v>-0.0002999999999957481</v>
+        <v>-0.9100000000000108</v>
       </c>
       <c r="I106">
-        <v>1.16001</v>
+        <v>9.0409</v>
       </c>
       <c r="J106">
-        <v>2.90788</v>
+        <v>0.0323</v>
       </c>
       <c r="K106">
-        <v>5.86338</v>
+        <v>-8.67731</v>
       </c>
       <c r="L106">
-        <v>8.82066</v>
+        <v>0.5564</v>
       </c>
       <c r="M106">
-        <v>15.03107</v>
+        <v>28.95142</v>
       </c>
       <c r="N106">
-        <v>24.54239</v>
+        <v>33.20402</v>
       </c>
       <c r="O106">
-        <v>21.44469</v>
+        <v>36.23359</v>
       </c>
       <c r="P106">
-        <v>30.75</v>
+        <v>54.48515</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.25">
@@ -6438,43 +6438,43 @@
         <v>1</v>
       </c>
       <c r="D107">
-        <v>85.97</v>
+        <v>537.44</v>
       </c>
       <c r="E107">
-        <v>0.1748</v>
+        <v>-1.0822</v>
       </c>
       <c r="F107">
-        <v>0.15</v>
+        <v>-5.88</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>-1.0878568667513333</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>-5.909999999999968</v>
       </c>
       <c r="I107">
-        <v>4.1837</v>
+        <v>7.81666</v>
       </c>
       <c r="J107">
-        <v>-1.42191</v>
+        <v>-1.40348</v>
       </c>
       <c r="K107">
-        <v>2.28197</v>
+        <v>0.69594</v>
       </c>
       <c r="L107">
-        <v>6.36523</v>
+        <v>10.39629</v>
       </c>
       <c r="M107">
-        <v>11.87459</v>
+        <v>56.03569</v>
       </c>
       <c r="N107">
-        <v>18.63122</v>
+        <v>85.1336</v>
       </c>
       <c r="O107">
-        <v>16.19868</v>
+        <v>80.69512</v>
       </c>
       <c r="P107">
-        <v>23.54266</v>
+        <v>126.65619</v>
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.25">
@@ -6488,43 +6488,43 @@
         <v>1</v>
       </c>
       <c r="D108">
-        <v>97.6</v>
+        <v>82.06</v>
       </c>
       <c r="E108">
-        <v>0.1745</v>
+        <v>-1.382</v>
       </c>
       <c r="F108">
-        <v>0.17</v>
+        <v>-1.15</v>
       </c>
       <c r="G108">
-        <v>0</v>
+        <v>-1.3820454272322935</v>
       </c>
       <c r="H108">
-        <v>0</v>
+        <v>-1.1499999999999915</v>
       </c>
       <c r="I108">
-        <v>0.11684</v>
+        <v>4.44724</v>
       </c>
       <c r="J108">
-        <v>-0.89046</v>
+        <v>2.55335</v>
       </c>
       <c r="K108">
-        <v>-0.13045</v>
+        <v>2.49014</v>
       </c>
       <c r="L108">
-        <v>-0.76019</v>
+        <v>6.79512</v>
       </c>
       <c r="M108">
-        <v>-0.68676</v>
+        <v>33.66559</v>
       </c>
       <c r="N108">
-        <v>0.11957</v>
+        <v>40.84364</v>
       </c>
       <c r="O108">
-        <v>-0.2041</v>
+        <v>46.91642</v>
       </c>
       <c r="P108">
-        <v>2.17268</v>
+        <v>82.17793</v>
       </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.25">
@@ -6538,43 +6538,43 @@
         <v>1</v>
       </c>
       <c r="D109">
-        <v>77.565</v>
+        <v>232.28</v>
       </c>
       <c r="E109">
-        <v>0.1356</v>
+        <v>-1.7262</v>
       </c>
       <c r="F109">
-        <v>0.105</v>
+        <v>-4.08</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>-1.780202122711323</v>
       </c>
       <c r="H109">
-        <v>0</v>
+        <v>-4.210000000000008</v>
       </c>
       <c r="I109">
-        <v>3.14193</v>
+        <v>9.17444</v>
       </c>
       <c r="J109">
-        <v>-2.42642</v>
+        <v>-2.22875</v>
       </c>
       <c r="K109">
-        <v>2.65349</v>
+        <v>-3.18919</v>
       </c>
       <c r="L109">
-        <v>9.75827</v>
+        <v>3.90148</v>
       </c>
       <c r="M109">
-        <v>27.60206</v>
+        <v>53.1046</v>
       </c>
       <c r="N109">
-        <v>29.82034</v>
+        <v>92.067</v>
       </c>
       <c r="O109">
-        <v>27.4817</v>
+        <v>82.69654</v>
       </c>
       <c r="P109">
-        <v>38.76973</v>
+        <v>144.06227</v>
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.25">
@@ -6588,43 +6588,43 @@
         <v>1</v>
       </c>
       <c r="D110">
-        <v>83.32</v>
+        <v>106.02</v>
       </c>
       <c r="E110">
-        <v>0.1202</v>
+        <v>-2.0148</v>
       </c>
       <c r="F110">
-        <v>0.1</v>
+        <v>-2.18</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>-1.9839875746537738</v>
       </c>
       <c r="H110">
-        <v>0</v>
+        <v>-2.146000000000001</v>
       </c>
       <c r="I110">
-        <v>2.96993</v>
+        <v>10.27942</v>
       </c>
       <c r="J110">
-        <v>3.39215</v>
+        <v>0.07403</v>
       </c>
       <c r="K110">
-        <v>10.38659</v>
+        <v>-11.17864</v>
       </c>
       <c r="L110">
-        <v>10.38659</v>
+        <v>-6.98435</v>
       </c>
       <c r="M110">
-        <v>14.39287</v>
+        <v>21.95782</v>
       </c>
       <c r="N110">
-        <v>25.39324</v>
+        <v>37.05957</v>
       </c>
       <c r="O110">
-        <v>20.33813</v>
+        <v>41.41493</v>
       </c>
       <c r="P110">
-        <v>31.7638</v>
+        <v>60.08244</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.25">
@@ -6638,43 +6638,43 @@
         <v>1</v>
       </c>
       <c r="D111">
-        <v>80.01</v>
+        <v>531.87</v>
       </c>
       <c r="E111">
-        <v>0.1001</v>
+        <v>-2.3823</v>
       </c>
       <c r="F111">
-        <v>0.08</v>
+        <v>-12.98</v>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>-2.350046817338931</v>
       </c>
       <c r="H111">
-        <v>0</v>
+        <v>-12.799999999999955</v>
       </c>
       <c r="I111">
-        <v>-0.05007</v>
+        <v>12.00887</v>
       </c>
       <c r="J111">
-        <v>2.97911</v>
+        <v>1.77553</v>
       </c>
       <c r="K111">
-        <v>6.55315</v>
+        <v>-4.60835</v>
       </c>
       <c r="L111">
-        <v>10.16437</v>
+        <v>4.00786</v>
       </c>
       <c r="M111">
-        <v>14.72499</v>
+        <v>51.93474</v>
       </c>
       <c r="N111">
-        <v>25.12474</v>
+        <v>67.0129</v>
       </c>
       <c r="O111">
-        <v>21.33246</v>
+        <v>69.71028</v>
       </c>
       <c r="P111">
-        <v>31.47837</v>
+        <v>104.10489</v>
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.25">
@@ -6688,43 +6688,43 @@
         <v>1</v>
       </c>
       <c r="D112">
-        <v>65.1931</v>
+        <v>135.81</v>
       </c>
       <c r="E112">
-        <v>-0.0509</v>
+        <v>-3.2037</v>
       </c>
       <c r="F112">
-        <v>-0.0332</v>
+        <v>-4.495</v>
       </c>
       <c r="G112">
-        <v>0.0001533907014607698</v>
+        <v>-3.1372549019607883</v>
       </c>
       <c r="H112">
-        <v>0.00010000000000331966</v>
+        <v>-4.400000000000006</v>
       </c>
       <c r="I112">
-        <v>4.11737</v>
+        <v>23.00349</v>
       </c>
       <c r="J112">
-        <v>-1.07914</v>
+        <v>-14.04211</v>
       </c>
       <c r="K112">
-        <v>0.61526</v>
+        <v>-22.26349</v>
       </c>
       <c r="L112">
-        <v>3.3979</v>
+        <v>-7.58956</v>
       </c>
       <c r="M112">
-        <v>10.16319</v>
+        <v>127.04756</v>
       </c>
       <c r="N112">
-        <v>23.31865</v>
+        <v>236.82216</v>
       </c>
       <c r="O112">
-        <v>16.69224</v>
+        <v>234.44786</v>
       </c>
       <c r="P112">
-        <v>32.92544</v>
+        <v>458.52138</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.25">
@@ -6738,43 +6738,43 @@
         <v>1</v>
       </c>
       <c r="D113">
-        <v>179.57</v>
+        <v>90.7</v>
       </c>
       <c r="E113">
-        <v>-1.0306</v>
+        <v>-3.2327</v>
       </c>
       <c r="F113">
-        <v>-1.87</v>
+        <v>-3.03</v>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>-3.1707056688374062</v>
       </c>
       <c r="H113">
-        <v>0</v>
+        <v>-2.969999999999999</v>
       </c>
       <c r="I113">
-        <v>7.09031</v>
+        <v>19.30725</v>
       </c>
       <c r="J113">
-        <v>11.9137</v>
+        <v>9.39067</v>
       </c>
       <c r="K113">
-        <v>34.68613</v>
+        <v>6.2275</v>
       </c>
       <c r="L113">
-        <v>38.38088</v>
+        <v>7.57529</v>
       </c>
       <c r="M113">
-        <v>21.61323</v>
+        <v>68.24451</v>
       </c>
       <c r="N113">
-        <v>22.87897</v>
+        <v>76.13597</v>
       </c>
       <c r="O113">
-        <v>10.11085</v>
+        <v>79.0673</v>
       </c>
       <c r="P113">
-        <v>25.24056</v>
+        <v>113.46141</v>
       </c>
     </row>
   </sheetData>
